--- a/data/2026_과천도시공사_제안목록_조직구조화.xlsx
+++ b/data/2026_과천도시공사_제안목록_조직구조화.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="2026_제안목록_142건" sheetId="1" r:id="rId1"/>
+    <sheet name="2026_제안목록_134건" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U143"/>
+  <dimension ref="A1:U135"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1507,70 +1507,69 @@
         <v/>
       </c>
     </row>
-    <row r="18" xml:space="preserve">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-03 07:16:00</v>
+        <v>2026-08-04 10:54:00</v>
       </c>
       <c r="D18" t="str">
-        <v>이동우</v>
+        <v>윤지혜</v>
       </c>
       <c r="E18" t="str">
-        <v>체육 5급</v>
+        <v>체육6급</v>
       </c>
       <c r="F18" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G18" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H18" t="str">
-        <v>수련관운영부</v>
+        <v>빙상부</v>
       </c>
       <c r="I18" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J18" t="str">
-        <v>지정제안</v>
+        <v>실행제안</v>
       </c>
       <c r="K18" t="str">
-        <v>안전</v>
+        <v>고객서비스</v>
       </c>
       <c r="L18" t="str">
-        <v>[지정제안] 안전취약 지역 비상벨 설치를 통한 안전사고 예방 및 신속 대응체계 구축</v>
+        <v>[실행제안]밀라노 동계올림픽 전광판 응원 이벤트 운영</v>
       </c>
       <c r="M18" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N18" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O18" t="str">
-        <v>수련관운영부</v>
+        <v>빙상부</v>
       </c>
       <c r="P18" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q18" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>중복 가능성 높음(채택)</v>
-      </c>
-      <c r="T18" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-06-080 화장실 및 탈의실 내 비상벨 설치를 통한 안전사고 예방 시스템 구축_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I71]</v>
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
       </c>
       <c r="U18" t="str">
-        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 화장실·탈의실에 비상벨을 설치하고 종합상황실과 연동하여 위급상황을 즉시 전달하는 제안임. 이번도 안전취약지역 중 탈의실 우선 설치가 핵심으로 대상·수단·효과가 겹침. 전수조사·위치번호·훈련 추가만으로 차별성이 충분한지 검토 필요.</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1578,10 +1577,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-04 10:54:00</v>
+        <v>2026-08-04 11:02:00</v>
       </c>
       <c r="D19" t="str">
         <v>윤지혜</v>
@@ -1602,25 +1601,25 @@
         <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J19" t="str">
-        <v>실행제안</v>
+        <v>자유제안</v>
       </c>
       <c r="K19" t="str">
         <v>고객서비스</v>
       </c>
       <c r="L19" t="str">
-        <v>[실행제안]밀라노 동계올림픽 전광판 응원 이벤트 운영</v>
+        <v>[자유제안] 엘리베이터 층별 안내 스티커 부착</v>
       </c>
       <c r="M19" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N19" t="str">
-        <v>시민회관체육운영처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O19" t="str">
-        <v>빙상부</v>
+        <v>시설기획부</v>
       </c>
       <c r="P19" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>시설관리처 시설기획부</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -1643,49 +1642,49 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-04 11:02:00</v>
+        <v>2026-08-04 11:32:00</v>
       </c>
       <c r="D20" t="str">
-        <v>윤지혜</v>
+        <v>김일권</v>
       </c>
       <c r="E20" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F20" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G20" t="str">
-        <v>시민회관체육운영처</v>
+        <v>시설관리처</v>
       </c>
       <c r="H20" t="str">
-        <v>빙상부</v>
+        <v>주차관리부</v>
       </c>
       <c r="I20" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>시설관리처 주차관리부</v>
       </c>
       <c r="J20" t="str">
-        <v>자유제안</v>
+        <v>지정제안</v>
       </c>
       <c r="K20" t="str">
-        <v>고객서비스</v>
+        <v>제도개선</v>
       </c>
       <c r="L20" t="str">
-        <v>[자유제안] 엘리베이터 층별 안내 스티커 부착</v>
+        <v>과천도시공사 비정규직관리지침 개정 요청</v>
       </c>
       <c r="M20" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N20" t="str">
-        <v>시설관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O20" t="str">
-        <v>시설기획부</v>
+        <v>인사부</v>
       </c>
       <c r="P20" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="Q20" t="str">
         <v/>
@@ -1708,13 +1707,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-04 11:32:00</v>
+        <v>2026-08-04 12:39:00</v>
       </c>
       <c r="D21" t="str">
-        <v>김일권</v>
+        <v>이승진</v>
       </c>
       <c r="E21" t="str">
         <v>기술6급</v>
@@ -1723,34 +1722,34 @@
         <v>운영관리본부</v>
       </c>
       <c r="G21" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H21" t="str">
-        <v>주차관리부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I21" t="str">
-        <v>시설관리처 주차관리부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J21" t="str">
         <v>지정제안</v>
       </c>
       <c r="K21" t="str">
-        <v>제도개선</v>
+        <v>안전</v>
       </c>
       <c r="L21" t="str">
-        <v>과천도시공사 비정규직관리지침 개정 요청</v>
+        <v>현장 근로자 휴대용 체감온도 측정기 지급</v>
       </c>
       <c r="M21" t="str">
-        <v>경영부문</v>
+        <v>사장 직속</v>
       </c>
       <c r="N21" t="str">
-        <v>경영지원실</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O21" t="str">
-        <v>인사부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P21" t="str">
-        <v>경영지원실 인사부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -1773,16 +1772,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-08-04 12:39:00</v>
+        <v>2026-08-05 21:20:00</v>
       </c>
       <c r="D22" t="str">
-        <v>이승진</v>
+        <v>권오형</v>
       </c>
       <c r="E22" t="str">
-        <v>기술6급</v>
+        <v>체육5급</v>
       </c>
       <c r="F22" t="str">
         <v>운영관리본부</v>
@@ -1791,31 +1790,31 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="H22" t="str">
-        <v>시설지원부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="I22" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="J22" t="str">
         <v>지정제안</v>
       </c>
       <c r="K22" t="str">
-        <v>안전</v>
+        <v>고객서비스</v>
       </c>
       <c r="L22" t="str">
-        <v>현장 근로자 휴대용 체감온도 측정기 지급</v>
+        <v>[지정제안] 수영장 노후 코스로프 및 안전형 턴버클 교체를 통한 레인시설 안전성 강화</v>
       </c>
       <c r="M22" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N22" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O22" t="str">
-        <v>안전총괄단</v>
+        <v>수련관운영부</v>
       </c>
       <c r="P22" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -1838,16 +1837,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-08-05 21:20:00</v>
+        <v>2026-08-06 10:18:00</v>
       </c>
       <c r="D23" t="str">
-        <v>권오형</v>
+        <v>김병철</v>
       </c>
       <c r="E23" t="str">
-        <v>체육5급</v>
+        <v>기술5급</v>
       </c>
       <c r="F23" t="str">
         <v>운영관리본부</v>
@@ -1865,10 +1864,10 @@
         <v>지정제안</v>
       </c>
       <c r="K23" t="str">
-        <v>고객서비스</v>
+        <v>안전</v>
       </c>
       <c r="L23" t="str">
-        <v>[지정제안] 수영장 노후 코스로프 및 안전형 턴버클 교체를 통한 레인시설 안전성 강화</v>
+        <v>청소년수련관 소화기 위치이동 금지 표지판 설치</v>
       </c>
       <c r="M23" t="str">
         <v>운영관리본부</v>
@@ -1877,10 +1876,10 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="O23" t="str">
-        <v>수련관운영부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P23" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -1903,16 +1902,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-08-06 10:18:00</v>
+        <v>2026-08-06 17:47:00</v>
       </c>
       <c r="D24" t="str">
-        <v>김병철</v>
+        <v>신상조</v>
       </c>
       <c r="E24" t="str">
-        <v>기술5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F24" t="str">
         <v>운영관리본부</v>
@@ -1930,10 +1929,10 @@
         <v>지정제안</v>
       </c>
       <c r="K24" t="str">
-        <v>안전</v>
+        <v>고객서비스</v>
       </c>
       <c r="L24" t="str">
-        <v>청소년수련관 소화기 위치이동 금지 표지판 설치</v>
+        <v>수영장 샤워장 출입구 안전거울 설치를 통한 이용객 안전 및 편의성 향상</v>
       </c>
       <c r="M24" t="str">
         <v>운영관리본부</v>
@@ -1942,10 +1941,10 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="O24" t="str">
-        <v>시설지원부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="P24" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="Q24" t="str">
         <v/>
@@ -1968,49 +1967,49 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-06 17:47:00</v>
+        <v>2026-08-07 09:10:00</v>
       </c>
       <c r="D25" t="str">
-        <v>신상조</v>
+        <v>박종용</v>
       </c>
       <c r="E25" t="str">
-        <v>체육5급</v>
+        <v>기술4급</v>
       </c>
       <c r="F25" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G25" t="str">
-        <v>공원수련관관리처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H25" t="str">
-        <v>수련관운영부</v>
+        <v>사업계획부</v>
       </c>
       <c r="I25" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>사업계획처 사업계획부</v>
       </c>
       <c r="J25" t="str">
         <v>지정제안</v>
       </c>
       <c r="K25" t="str">
-        <v>고객서비스</v>
+        <v>업무개선</v>
       </c>
       <c r="L25" t="str">
-        <v>수영장 샤워장 출입구 안전거울 설치를 통한 이용객 안전 및 편의성 향상</v>
+        <v>개발사업 통합 리스크 관리체계 구축</v>
       </c>
       <c r="M25" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N25" t="str">
-        <v>공원수련관관리처</v>
+        <v>사업계획처</v>
       </c>
       <c r="O25" t="str">
-        <v>수련관운영부</v>
+        <v>사업계획부</v>
       </c>
       <c r="P25" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>사업계획처 사업계획부</v>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -2033,49 +2032,49 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-07 09:10:00</v>
+        <v>2026-08-07 18:21:00</v>
       </c>
       <c r="D26" t="str">
-        <v>박종용</v>
+        <v>장영수</v>
       </c>
       <c r="E26" t="str">
-        <v>기술4급</v>
+        <v>행정4급</v>
       </c>
       <c r="F26" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G26" t="str">
-        <v>사업계획처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H26" t="str">
-        <v>사업계획부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I26" t="str">
-        <v>사업계획처 사업계획부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J26" t="str">
         <v>지정제안</v>
       </c>
       <c r="K26" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L26" t="str">
-        <v>개발사업 통합 리스크 관리체계 구축</v>
+        <v>UPS 배터리 관리 시스템(BMS) 도입을 통한 화재 예방</v>
       </c>
       <c r="M26" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N26" t="str">
-        <v>사업계획처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O26" t="str">
-        <v>사업계획부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P26" t="str">
-        <v>사업계획처 사업계획부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q26" t="str">
         <v/>
@@ -2098,49 +2097,49 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-07 18:21:00</v>
+        <v>2026-08-10 08:18:00</v>
       </c>
       <c r="D27" t="str">
-        <v>장영수</v>
+        <v>이성준</v>
       </c>
       <c r="E27" t="str">
-        <v>행정4급</v>
+        <v>행정5급</v>
       </c>
       <c r="F27" t="str">
-        <v>경영부문</v>
+        <v>사장 직속</v>
       </c>
       <c r="G27" t="str">
-        <v>경영지원실</v>
+        <v>청렴감사단</v>
       </c>
       <c r="H27" t="str">
-        <v>총무행정부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="I27" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="J27" t="str">
         <v>지정제안</v>
       </c>
       <c r="K27" t="str">
-        <v>안전</v>
+        <v>AI혁신</v>
       </c>
       <c r="L27" t="str">
-        <v>UPS 배터리 관리 시스템(BMS) 도입을 통한 화재 예방</v>
+        <v>[지정제안] 감사·리스크 AI에이전트 구축 활용을 통한 업무 효율 증대</v>
       </c>
       <c r="M27" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N27" t="str">
-        <v>시설관리처</v>
+        <v>청렴감사단</v>
       </c>
       <c r="O27" t="str">
-        <v>시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="P27" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="Q27" t="str">
         <v/>
@@ -2163,28 +2162,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-10 08:18:00</v>
+        <v>2026-08-10 14:04:00</v>
       </c>
       <c r="D28" t="str">
-        <v>이성준</v>
+        <v>김민정</v>
       </c>
       <c r="E28" t="str">
-        <v>행정5급</v>
+        <v>체육6급</v>
       </c>
       <c r="F28" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G28" t="str">
-        <v>청렴감사단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H28" t="str">
-        <v>청렴감사단</v>
+        <v>수영부</v>
       </c>
       <c r="I28" t="str">
-        <v>청렴감사단</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J28" t="str">
         <v>지정제안</v>
@@ -2193,19 +2192,19 @@
         <v>AI혁신</v>
       </c>
       <c r="L28" t="str">
-        <v>[지정제안] 감사·리스크 AI에이전트 구축 활용을 통한 업무 효율 증대</v>
+        <v>[지정제안] AI 신규회원 스마트 적응 시뮬레이션 구축</v>
       </c>
       <c r="M28" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N28" t="str">
-        <v>청렴감사단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O28" t="str">
-        <v>청렴감사단</v>
+        <v>수영부</v>
       </c>
       <c r="P28" t="str">
-        <v>청렴감사단</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -2228,49 +2227,49 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-10 14:04:00</v>
+        <v>2026-08-10 19:48:00</v>
       </c>
       <c r="D29" t="str">
-        <v>김민정</v>
+        <v>윤귀환</v>
       </c>
       <c r="E29" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F29" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G29" t="str">
-        <v>시민회관체육운영처</v>
+        <v>시설관리처</v>
       </c>
       <c r="H29" t="str">
-        <v>수영부</v>
+        <v>시설운영부</v>
       </c>
       <c r="I29" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="J29" t="str">
         <v>지정제안</v>
       </c>
       <c r="K29" t="str">
-        <v>AI혁신</v>
+        <v>안전</v>
       </c>
       <c r="L29" t="str">
-        <v>[지정제안] AI 신규회원 스마트 적응 시뮬레이션 구축</v>
+        <v>[지정제안] 친환경 수질관리 설비 도입을 통한 근로자·이용객 안전사고 예방 강화</v>
       </c>
       <c r="M29" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N29" t="str">
-        <v>시민회관체육운영처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O29" t="str">
-        <v>수영부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P29" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q29" t="str">
         <v/>
@@ -2288,21 +2287,21 @@
         <v/>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-10 15:16:00</v>
+        <v>2026-08-12 15:47:00</v>
       </c>
       <c r="D30" t="str">
-        <v>박왕권</v>
+        <v>윤승현</v>
       </c>
       <c r="E30" t="str">
-        <v>기술4급</v>
+        <v>기술5급</v>
       </c>
       <c r="F30" t="str">
         <v>운영관리본부</v>
@@ -2311,19 +2310,19 @@
         <v>시설관리처</v>
       </c>
       <c r="H30" t="str">
-        <v>시설운영부</v>
+        <v>시설기획부</v>
       </c>
       <c r="I30" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>시설관리처 시설기획부</v>
       </c>
       <c r="J30" t="str">
         <v>지정제안</v>
       </c>
       <c r="K30" t="str">
-        <v>안전</v>
+        <v>AI혁신</v>
       </c>
       <c r="L30" t="str">
-        <v>선제적 제습관리를 통한 시민회관 결로 예방 및 시설환경 개선</v>
+        <v>(소규모 공사 설계업무) AI 이미지 시각화 기반 공간 연출 및 신속한 의사결정 체계</v>
       </c>
       <c r="M30" t="str">
         <v>운영관리본부</v>
@@ -2332,26 +2331,25 @@
         <v>시설관리처</v>
       </c>
       <c r="O30" t="str">
-        <v>시설운영부</v>
+        <v>시설기획부</v>
       </c>
       <c r="P30" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>시설관리처 시설기획부</v>
       </c>
       <c r="Q30" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>중복 가능성 높음(채택)</v>
-      </c>
-      <c r="T30" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-07-101 시민회관 지하층 결로 방지 위한 제습기 설치_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I91]</v>
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
       </c>
       <c r="U30" t="str">
-        <v>2025-07-101의 심사결과가 채택임. 시민회관 동일 주요 출입구 5개소의 산업용 제습기 설치·24시간 운전·공조 병행·빙상장 관람창 결로 방지가 일치함. 단가·효과검증·중앙계단 추가는 보완 요소임. 2023-06-012는 채택결과 미확인으로 판단 근거에서 제외함.</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -2359,49 +2357,49 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-08-10 19:48:00</v>
+        <v>2026-08-12 17:50:00</v>
       </c>
       <c r="D31" t="str">
-        <v>윤귀환</v>
+        <v>최성호</v>
       </c>
       <c r="E31" t="str">
-        <v>기술6급</v>
+        <v>기술5급</v>
       </c>
       <c r="F31" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G31" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H31" t="str">
-        <v>시설운영부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I31" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J31" t="str">
         <v>지정제안</v>
       </c>
       <c r="K31" t="str">
-        <v>안전</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L31" t="str">
-        <v>[지정제안] 친환경 수질관리 설비 도입을 통한 근로자·이용객 안전사고 예방 강화</v>
+        <v>[지정제안]조경자재·약제 구매단가 데이터화를 통한 예산절감 방안</v>
       </c>
       <c r="M31" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N31" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O31" t="str">
-        <v>시설운영부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P31" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q31" t="str">
         <v/>
@@ -2424,49 +2422,49 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-08-12 15:47:00</v>
+        <v>2026-08-13 11:44:00</v>
       </c>
       <c r="D32" t="str">
-        <v>윤승현</v>
+        <v>김동환</v>
       </c>
       <c r="E32" t="str">
-        <v>기술5급</v>
+        <v>기술6급</v>
       </c>
       <c r="F32" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G32" t="str">
-        <v>시설관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H32" t="str">
-        <v>시설기획부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I32" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J32" t="str">
         <v>지정제안</v>
       </c>
       <c r="K32" t="str">
-        <v>AI혁신</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L32" t="str">
-        <v>(소규모 공사 설계업무) AI 이미지 시각화 기반 공간 연출 및 신속한 의사결정 체계</v>
+        <v>[지정제안] 공사 불용(폐기) 물품 처리절차 개선 방안</v>
       </c>
       <c r="M32" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N32" t="str">
-        <v>시설관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O32" t="str">
-        <v>시설기획부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P32" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q32" t="str">
         <v/>
@@ -2489,49 +2487,49 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-08-12 17:50:00</v>
+        <v>2026-08-13 09:45:00</v>
       </c>
       <c r="D33" t="str">
-        <v>최성호</v>
+        <v>황광엽</v>
       </c>
       <c r="E33" t="str">
-        <v>기술5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F33" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G33" t="str">
-        <v>공원수련관관리처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H33" t="str">
-        <v>시설지원부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I33" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="J33" t="str">
-        <v>지정제안</v>
+        <v>실행제안</v>
       </c>
       <c r="K33" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>업무개선</v>
       </c>
       <c r="L33" t="str">
-        <v>[지정제안]조경자재·약제 구매단가 데이터화를 통한 예산절감 방안</v>
+        <v>(실행제안)과천과천 공공주택지구 이주촉진 및 현장관리 전문지원체계 구축</v>
       </c>
       <c r="M33" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N33" t="str">
-        <v>공원수련관관리처</v>
+        <v>사업계획처</v>
       </c>
       <c r="O33" t="str">
-        <v>시설지원부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="P33" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="Q33" t="str">
         <v/>
@@ -2554,49 +2552,49 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-08-13 11:44:00</v>
+        <v>2026-08-13 09:48:00</v>
       </c>
       <c r="D34" t="str">
-        <v>김동환</v>
+        <v>최성호</v>
       </c>
       <c r="E34" t="str">
-        <v>기술6급</v>
+        <v>기술5급</v>
       </c>
       <c r="F34" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G34" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H34" t="str">
-        <v>총무행정부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I34" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J34" t="str">
-        <v>지정제안</v>
+        <v>실행제안</v>
       </c>
       <c r="K34" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>시설개선</v>
       </c>
       <c r="L34" t="str">
-        <v>[지정제안] 공사 불용(폐기) 물품 처리절차 개선 방안</v>
+        <v>[실행제안] 관문체육공원 고사 느티나무 하부 녹지대 경관 정원 조성</v>
       </c>
       <c r="M34" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N34" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O34" t="str">
-        <v>총무행정부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P34" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q34" t="str">
         <v/>
@@ -2614,54 +2612,54 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-08-13 09:45:00</v>
+        <v>2026-08-13 09:51:00</v>
       </c>
       <c r="D35" t="str">
-        <v>황광엽</v>
+        <v>최성호</v>
       </c>
       <c r="E35" t="str">
-        <v>체육5급</v>
+        <v>기술5급</v>
       </c>
       <c r="F35" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G35" t="str">
-        <v>사업계획처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H35" t="str">
-        <v>판매·보상부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I35" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J35" t="str">
         <v>실행제안</v>
       </c>
       <c r="K35" t="str">
-        <v>업무개선</v>
+        <v>시설개선</v>
       </c>
       <c r="L35" t="str">
-        <v>(실행제안)과천과천 공공주택지구 이주촉진 및 현장관리 전문지원체계 구축</v>
+        <v>[실행제안] 관문체육공원 녹지대 저관리형 정원 조성</v>
       </c>
       <c r="M35" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N35" t="str">
-        <v>사업계획처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O35" t="str">
-        <v>판매·보상부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P35" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q35" t="str">
         <v/>
@@ -2670,13 +2668,14 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v/>
-      </c>
-      <c r="T35" t="str">
-        <v/>
+        <v>유사(채택)</v>
+      </c>
+      <c r="T35" t="str" xml:space="preserve">
+        <v xml:space="preserve">2025-06-075 로우-메인터넌스 조경(Low-Maintenance:저관리형) 도입_x000d_
+심사결과: 채택 [2025년 제안 총괄 !I66]</v>
       </c>
       <c r="U35" t="str">
-        <v/>
+        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 다년생·자생식물 위주 식재로 매년 재식재와 관리비를 줄이는 저관리형 조경을 제안함. 이번은 관문공원 화단에 다년생·상록 소교목을 식재하여 같은 원리를 실행하되 메주석 경계 재시공과 구체적 적용 장소가 추가됨.</v>
       </c>
     </row>
     <row r="36">
@@ -2684,49 +2683,49 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-08-13 09:48:00</v>
+        <v>2026-08-13 11:28:00</v>
       </c>
       <c r="D36" t="str">
-        <v>최성호</v>
+        <v>김혜경</v>
       </c>
       <c r="E36" t="str">
-        <v>기술5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F36" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G36" t="str">
-        <v>공원수련관관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H36" t="str">
-        <v>시설지원부</v>
+        <v>인사부</v>
       </c>
       <c r="I36" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="J36" t="str">
-        <v>실행제안</v>
+        <v>지정제안</v>
       </c>
       <c r="K36" t="str">
-        <v>시설개선</v>
+        <v>AI혁신</v>
       </c>
       <c r="L36" t="str">
-        <v>[실행제안] 관문체육공원 고사 느티나무 하부 녹지대 경관 정원 조성</v>
+        <v>[지정제안] AI 기반 사규 개정업무 업무혁신</v>
       </c>
       <c r="M36" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N36" t="str">
-        <v>공원수련관관리처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O36" t="str">
-        <v>시설지원부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="P36" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="Q36" t="str">
         <v/>
@@ -2744,54 +2743,54 @@
         <v/>
       </c>
     </row>
-    <row r="37" xml:space="preserve">
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-08-13 09:51:00</v>
+        <v>2026-08-13 11:33:00</v>
       </c>
       <c r="D37" t="str">
-        <v>최성호</v>
+        <v>김혜경</v>
       </c>
       <c r="E37" t="str">
-        <v>기술5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F37" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G37" t="str">
-        <v>공원수련관관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H37" t="str">
-        <v>시설지원부</v>
+        <v>인사부</v>
       </c>
       <c r="I37" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="J37" t="str">
-        <v>실행제안</v>
+        <v>지정제안</v>
       </c>
       <c r="K37" t="str">
-        <v>시설개선</v>
+        <v>AI혁신</v>
       </c>
       <c r="L37" t="str">
-        <v>[실행제안] 관문체육공원 녹지대 저관리형 정원 조성</v>
+        <v>[지정제안]사규 학습 퀴즈앱 도입</v>
       </c>
       <c r="M37" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N37" t="str">
-        <v>공원수련관관리처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O37" t="str">
-        <v>시설지원부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="P37" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="Q37" t="str">
         <v/>
@@ -2800,14 +2799,13 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T37" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-06-075 로우-메인터넌스 조경(Low-Maintenance:저관리형) 도입_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I66]</v>
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
       </c>
       <c r="U37" t="str">
-        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 다년생·자생식물 위주 식재로 매년 재식재와 관리비를 줄이는 저관리형 조경을 제안함. 이번은 관문공원 화단에 다년생·상록 소교목을 식재하여 같은 원리를 실행하되 메주석 경계 재시공과 구체적 적용 장소가 추가됨.</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2815,49 +2813,49 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-08-13 11:28:00</v>
+        <v>2026-08-13 16:22:00</v>
       </c>
       <c r="D38" t="str">
-        <v>김혜경</v>
+        <v>이호형</v>
       </c>
       <c r="E38" t="str">
-        <v>체육5급</v>
+        <v>체육6급</v>
       </c>
       <c r="F38" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G38" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H38" t="str">
-        <v>인사부</v>
+        <v>공원운영부</v>
       </c>
       <c r="I38" t="str">
-        <v>경영지원실 인사부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="J38" t="str">
         <v>지정제안</v>
       </c>
       <c r="K38" t="str">
-        <v>AI혁신</v>
+        <v>안전</v>
       </c>
       <c r="L38" t="str">
-        <v>[지정제안] AI 기반 사규 개정업무 업무혁신</v>
+        <v>[지정제안] 헬스장 트레드밀(런닝머신) 안전사고 예방</v>
       </c>
       <c r="M38" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N38" t="str">
-        <v>미래전략실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O38" t="str">
-        <v>미래혁신부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P38" t="str">
-        <v>미래전략실 미래혁신부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q38" t="str">
         <v/>
@@ -2880,49 +2878,49 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-08-13 11:33:00</v>
+        <v>2026-09-18 16:01:00</v>
       </c>
       <c r="D39" t="str">
-        <v>김혜경</v>
+        <v>박명진</v>
       </c>
       <c r="E39" t="str">
-        <v>체육5급</v>
+        <v>행정5급</v>
       </c>
       <c r="F39" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G39" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H39" t="str">
-        <v>인사부</v>
+        <v>공원운영부</v>
       </c>
       <c r="I39" t="str">
-        <v>경영지원실 인사부</v>
+        <v>공원수련관관리처 박명진</v>
       </c>
       <c r="J39" t="str">
         <v>지정제안</v>
       </c>
       <c r="K39" t="str">
-        <v>AI혁신</v>
+        <v>업무개선</v>
       </c>
       <c r="L39" t="str">
-        <v>[지정제안]사규 학습 퀴즈앱 도입</v>
+        <v>[지정제안]유실물 처리 내부 매뉴얼(개선)</v>
       </c>
       <c r="M39" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N39" t="str">
-        <v>미래전략실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O39" t="str">
-        <v>미래혁신부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P39" t="str">
-        <v>미래전략실 미래혁신부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q39" t="str">
         <v/>
@@ -2945,49 +2943,49 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-08-13 16:22:00</v>
+        <v>2026-08-14 15:11:00</v>
       </c>
       <c r="D40" t="str">
-        <v>이호형</v>
+        <v>이영권</v>
       </c>
       <c r="E40" t="str">
-        <v>체육6급</v>
+        <v>기술5급</v>
       </c>
       <c r="F40" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G40" t="str">
-        <v>공원수련관관리처</v>
+        <v>시설관리처</v>
       </c>
       <c r="H40" t="str">
-        <v>공원운영부</v>
+        <v>시설운영부</v>
       </c>
       <c r="I40" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="J40" t="str">
         <v>지정제안</v>
       </c>
       <c r="K40" t="str">
-        <v>안전</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L40" t="str">
-        <v>[지정제안] 헬스장 트레드밀(런닝머신) 안전사고 예방</v>
+        <v>[지정제안]공사 내 폐소화기 무상처리를 통한 처리비용 및 예산절감</v>
       </c>
       <c r="M40" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N40" t="str">
-        <v>공원수련관관리처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O40" t="str">
-        <v>공원운영부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P40" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q40" t="str">
         <v/>
@@ -3010,49 +3008,49 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-09-18 16:01:00</v>
+        <v>2026-08-14 21:16:00</v>
       </c>
       <c r="D41" t="str">
-        <v>박명진</v>
+        <v>이호연</v>
       </c>
       <c r="E41" t="str">
-        <v>행정5급</v>
+        <v>행정6급</v>
       </c>
       <c r="F41" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="G41" t="str">
-        <v>공원수련관관리처</v>
+        <v>청렴감사단</v>
       </c>
       <c r="H41" t="str">
-        <v>공원운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="I41" t="str">
-        <v>공원수련관관리처 박명진</v>
+        <v>청렴감사단</v>
       </c>
       <c r="J41" t="str">
         <v>지정제안</v>
       </c>
       <c r="K41" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L41" t="str">
-        <v>[지정제안]유실물 처리 내부 매뉴얼(개선)</v>
+        <v>[지정제안]장애인 도움벨 설치</v>
       </c>
       <c r="M41" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N41" t="str">
-        <v>공원수련관관리처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O41" t="str">
-        <v>공원운영부</v>
+        <v>시설기획부</v>
       </c>
       <c r="P41" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시설관리처 시설기획부</v>
       </c>
       <c r="Q41" t="str">
         <v/>
@@ -3075,49 +3073,49 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-08-14 15:11:00</v>
+        <v>2026-08-18 11:41:00</v>
       </c>
       <c r="D42" t="str">
-        <v>이영권</v>
+        <v>박인숙</v>
       </c>
       <c r="E42" t="str">
-        <v>기술5급</v>
+        <v>행정4급</v>
       </c>
       <c r="F42" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="G42" t="str">
-        <v>시설관리처</v>
+        <v>청렴감사단</v>
       </c>
       <c r="H42" t="str">
-        <v>시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="I42" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="J42" t="str">
         <v>지정제안</v>
       </c>
       <c r="K42" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>제도개선</v>
       </c>
       <c r="L42" t="str">
-        <v>[지정제안]공사 내 폐소화기 무상처리를 통한 처리비용 및 예산절감</v>
+        <v>[지정제안] 외부 전문기관 연계 「익명신고센터」 운영</v>
       </c>
       <c r="M42" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N42" t="str">
-        <v>시설관리처</v>
+        <v>청렴감사단</v>
       </c>
       <c r="O42" t="str">
-        <v>시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="P42" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -3140,16 +3138,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-08-14 21:16:00</v>
+        <v>2026-08-18 13:08:00</v>
       </c>
       <c r="D43" t="str">
-        <v>이호연</v>
+        <v>박인숙</v>
       </c>
       <c r="E43" t="str">
-        <v>행정6급</v>
+        <v>행정4급</v>
       </c>
       <c r="F43" t="str">
         <v>사장 직속</v>
@@ -3167,22 +3165,22 @@
         <v>지정제안</v>
       </c>
       <c r="K43" t="str">
-        <v>안전</v>
+        <v>제도개선</v>
       </c>
       <c r="L43" t="str">
-        <v>[지정제안]장애인 도움벨 설치</v>
+        <v>[지정제안] AI 활용 업무 「인권리스크 사전점검제」 운영</v>
       </c>
       <c r="M43" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N43" t="str">
-        <v>시설관리처</v>
+        <v>청렴감사단</v>
       </c>
       <c r="O43" t="str">
-        <v>시설기획부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="P43" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>청렴감사단</v>
       </c>
       <c r="Q43" t="str">
         <v/>
@@ -3205,49 +3203,49 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-08-18 11:41:00</v>
+        <v>2026-08-19 08:57:00</v>
       </c>
       <c r="D44" t="str">
-        <v>박인숙</v>
+        <v>황광엽</v>
       </c>
       <c r="E44" t="str">
-        <v>행정4급</v>
+        <v>체육5급</v>
       </c>
       <c r="F44" t="str">
-        <v>사장 직속</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G44" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처</v>
       </c>
       <c r="H44" t="str">
-        <v>청렴감사단</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I44" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="J44" t="str">
         <v>지정제안</v>
       </c>
       <c r="K44" t="str">
-        <v>제도개선</v>
+        <v>사규 개정 및 제도 개선</v>
       </c>
       <c r="L44" t="str">
-        <v>[지정제안] 외부 전문기관 연계 「익명신고센터」 운영</v>
+        <v>[지정제안]소송업무 처리절차 간소화 및 이사회 의결대상 명확화</v>
       </c>
       <c r="M44" t="str">
-        <v>사장 직속</v>
+        <v>경영부문</v>
       </c>
       <c r="N44" t="str">
-        <v>청렴감사단</v>
+        <v>경영지원실</v>
       </c>
       <c r="O44" t="str">
-        <v>청렴감사단</v>
+        <v>인사부</v>
       </c>
       <c r="P44" t="str">
-        <v>청렴감사단</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="Q44" t="str">
         <v/>
@@ -3270,49 +3268,49 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" t="str">
-        <v>2026-08-18 13:08:00</v>
+        <v>2026-08-19 10:31:00</v>
       </c>
       <c r="D45" t="str">
-        <v>박인숙</v>
+        <v>성연우</v>
       </c>
       <c r="E45" t="str">
         <v>행정4급</v>
       </c>
       <c r="F45" t="str">
-        <v>사장 직속</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G45" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처</v>
       </c>
       <c r="H45" t="str">
-        <v>청렴감사단</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I45" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="J45" t="str">
         <v>지정제안</v>
       </c>
       <c r="K45" t="str">
-        <v>제도개선</v>
+        <v>지역상생·협력</v>
       </c>
       <c r="L45" t="str">
-        <v>[지정제안] AI 활용 업무 「인권리스크 사전점검제」 운영</v>
+        <v>[지정제안] 기업유치·민간협력 강화를 위한 「GCUC 기업·투자 파트너 등록제」 도입</v>
       </c>
       <c r="M45" t="str">
-        <v>사장 직속</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N45" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처</v>
       </c>
       <c r="O45" t="str">
-        <v>청렴감사단</v>
+        <v>판매·보상부</v>
       </c>
       <c r="P45" t="str">
-        <v>청렴감사단</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -3335,49 +3333,49 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C46" t="str">
-        <v>2026-08-19 08:57:00</v>
+        <v>2026-08-19 17:37:00</v>
       </c>
       <c r="D46" t="str">
-        <v>황광엽</v>
+        <v>정옥환</v>
       </c>
       <c r="E46" t="str">
-        <v>체육5급</v>
+        <v>행정6급</v>
       </c>
       <c r="F46" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G46" t="str">
-        <v>사업계획처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H46" t="str">
-        <v>판매·보상부</v>
+        <v>인사부</v>
       </c>
       <c r="I46" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="J46" t="str">
         <v>지정제안</v>
       </c>
       <c r="K46" t="str">
-        <v>사규 개정 및 제도 개선</v>
+        <v>안전</v>
       </c>
       <c r="L46" t="str">
-        <v>[지정제안]소송업무 처리절차 간소화 및 이사회 의결대상 명확화</v>
+        <v>[지정제안]저비용·고효율 주차안전 개선을 위한 「수직(입체형) 주차유도선」 시범 도입</v>
       </c>
       <c r="M46" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N46" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O46" t="str">
-        <v>인사부</v>
+        <v>주차관리부</v>
       </c>
       <c r="P46" t="str">
-        <v>경영지원실 인사부</v>
+        <v>시설관리처 주차관리부</v>
       </c>
       <c r="Q46" t="str">
         <v/>
@@ -3395,54 +3393,54 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" t="str">
-        <v>2026-08-19 10:31:00</v>
+        <v>2026-08-20 13:32:00</v>
       </c>
       <c r="D47" t="str">
-        <v>성연우</v>
+        <v>배종윤</v>
       </c>
       <c r="E47" t="str">
-        <v>행정4급</v>
+        <v>체육6급</v>
       </c>
       <c r="F47" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G47" t="str">
-        <v>사업계획처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H47" t="str">
-        <v>판매·보상부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I47" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="J47" t="str">
         <v>지정제안</v>
       </c>
       <c r="K47" t="str">
-        <v>지역상생·협력</v>
+        <v>안전</v>
       </c>
       <c r="L47" t="str">
-        <v>[지정제안] 기업유치·민간협력 강화를 위한 「GCUC 기업·투자 파트너 등록제」 도입</v>
+        <v>[지정제안]운동기구 위험도 표시제(안전사고 예방을 위한 관리 강화 및 개선방안)</v>
       </c>
       <c r="M47" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N47" t="str">
-        <v>사업계획처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O47" t="str">
-        <v>판매·보상부</v>
+        <v>여가체육부</v>
       </c>
       <c r="P47" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="Q47" t="str">
         <v/>
@@ -3451,147 +3449,147 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v/>
-      </c>
-      <c r="T47" t="str">
-        <v/>
-      </c>
-      <c r="U47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>54</v>
-      </c>
-      <c r="C48" t="str">
-        <v>2026-08-19 17:37:00</v>
-      </c>
-      <c r="D48" t="str">
-        <v>정옥환</v>
-      </c>
-      <c r="E48" t="str">
-        <v>행정6급</v>
-      </c>
-      <c r="F48" t="str">
-        <v>경영부문</v>
-      </c>
-      <c r="G48" t="str">
-        <v>경영지원실</v>
-      </c>
-      <c r="H48" t="str">
-        <v>인사부</v>
-      </c>
-      <c r="I48" t="str">
-        <v>경영지원실 인사부</v>
-      </c>
-      <c r="J48" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K48" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L48" t="str">
-        <v>[지정제안]저비용·고효율 주차안전 개선을 위한 「수직(입체형) 주차유도선」 시범 도입</v>
-      </c>
-      <c r="M48" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N48" t="str">
-        <v>시설관리처</v>
-      </c>
-      <c r="O48" t="str">
-        <v>주차관리부</v>
-      </c>
-      <c r="P48" t="str">
-        <v>시설관리처 주차관리부</v>
-      </c>
-      <c r="Q48" t="str">
-        <v/>
-      </c>
-      <c r="R48" t="str">
-        <v/>
-      </c>
-      <c r="S48" t="str">
-        <v/>
-      </c>
-      <c r="T48" t="str">
-        <v/>
-      </c>
-      <c r="U48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>55</v>
-      </c>
-      <c r="C49" t="str">
-        <v>2026-08-20 13:32:00</v>
-      </c>
-      <c r="D49" t="str">
-        <v>배종윤</v>
-      </c>
-      <c r="E49" t="str">
-        <v>체육6급</v>
-      </c>
-      <c r="F49" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G49" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H49" t="str">
-        <v>여가체육부</v>
-      </c>
-      <c r="I49" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
-      </c>
-      <c r="J49" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K49" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L49" t="str">
-        <v>[지정제안]운동기구 위험도 표시제(안전사고 예방을 위한 관리 강화 및 개선방안)</v>
-      </c>
-      <c r="M49" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N49" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="O49" t="str">
-        <v>여가체육부</v>
-      </c>
-      <c r="P49" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
-      </c>
-      <c r="Q49" t="str">
-        <v/>
-      </c>
-      <c r="R49" t="str">
-        <v/>
-      </c>
-      <c r="S49" t="str">
         <v>판단보류(채택결과 미확인)</v>
       </c>
-      <c r="T49" t="str" xml:space="preserve">
+      <c r="T47" t="str" xml:space="preserve">
         <v xml:space="preserve">2023-11-104 2023년글로벌정책추진국외연수_헬스장 운동기구 안전표시 개선_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]_x000d_
 _x000d_
 2022-12-180 근력운동기구 안전선 표기_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]</v>
       </c>
+      <c r="U47" t="str">
+        <v>기구 안전표시·안전선 표기와 유사하지만 두 비교안의 채택결과를 확인할 수 없음. 또한 2023년 제안은 첨부 참조뿐이어서 위험등급 스티커와 단순 안전선 표시의 차이를 원문으로 확인해야 함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>56</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2026-08-21 11:46:00</v>
+      </c>
+      <c r="D48" t="str">
+        <v>지하연</v>
+      </c>
+      <c r="E48" t="str">
+        <v>행정6급</v>
+      </c>
+      <c r="F48" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G48" t="str">
+        <v>시설관리처</v>
+      </c>
+      <c r="H48" t="str">
+        <v>시설기획부</v>
+      </c>
+      <c r="I48" t="str">
+        <v>시설관리처 시설기획부</v>
+      </c>
+      <c r="J48" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K48" t="str">
+        <v>제도개선</v>
+      </c>
+      <c r="L48" t="str">
+        <v>[지정제안] 시계탑광장 대관 및 운영기준 제도화를 통한 시민 이용편의 향상과 행정 효율성 제고</v>
+      </c>
+      <c r="M48" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N48" t="str">
+        <v>시설관리처</v>
+      </c>
+      <c r="O48" t="str">
+        <v>시설기획부</v>
+      </c>
+      <c r="P48" t="str">
+        <v>시설관리처 시설기획부</v>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
+        <v/>
+      </c>
+      <c r="T48" t="str">
+        <v/>
+      </c>
+      <c r="U48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>57</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2026-08-21 13:59:00</v>
+      </c>
+      <c r="D49" t="str">
+        <v>양다혜</v>
+      </c>
+      <c r="E49" t="str">
+        <v>행정6급</v>
+      </c>
+      <c r="F49" t="str">
+        <v>개발사업본부</v>
+      </c>
+      <c r="G49" t="str">
+        <v>사업계획처</v>
+      </c>
+      <c r="H49" t="str">
+        <v>판매·보상부</v>
+      </c>
+      <c r="I49" t="str">
+        <v>사업계획처 판매보상부</v>
+      </c>
+      <c r="J49" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K49" t="str">
+        <v>지역상생</v>
+      </c>
+      <c r="L49" t="str">
+        <v>[지정제안] 시민회관 열린광장 프로젝트(공공공간 활용한 지역상생·민관협력형 생활문화공간 조성)</v>
+      </c>
+      <c r="M49" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N49" t="str">
+        <v>시민회관체육운영처</v>
+      </c>
+      <c r="O49" t="str">
+        <v>여가체육부</v>
+      </c>
+      <c r="P49" t="str">
+        <v>시민회관체육운영처 여가체육부</v>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
+        <v/>
+      </c>
+      <c r="T49" t="str">
+        <v/>
+      </c>
       <c r="U49" t="str">
-        <v>기구 안전표시·안전선 표기와 유사하지만 두 비교안의 채택결과를 확인할 수 없음. 또한 2023년 제안은 첨부 참조뿐이어서 위험등급 스티커와 단순 안전선 표시의 차이를 원문으로 확인해야 함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3599,49 +3597,49 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" t="str">
-        <v>2026-08-21 11:46:00</v>
+        <v>2026-08-21 16:42:00</v>
       </c>
       <c r="D50" t="str">
-        <v>지하연</v>
+        <v>최민기</v>
       </c>
       <c r="E50" t="str">
-        <v>행정6급</v>
+        <v>업무직</v>
       </c>
       <c r="F50" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G50" t="str">
-        <v>시설관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H50" t="str">
-        <v>시설기획부</v>
+        <v>빙상부</v>
       </c>
       <c r="I50" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J50" t="str">
         <v>지정제안</v>
       </c>
       <c r="K50" t="str">
-        <v>제도개선</v>
+        <v>안전</v>
       </c>
       <c r="L50" t="str">
-        <v>[지정제안] 시계탑광장 대관 및 운영기준 제도화를 통한 시민 이용편의 향상과 행정 효율성 제고</v>
+        <v>[지정제안] 지하 2층 빙상장 복도 화장실 앞 충돌방지(미끄럼방지 겸용) 스티커 부착</v>
       </c>
       <c r="M50" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N50" t="str">
-        <v>시설관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O50" t="str">
-        <v>시설기획부</v>
+        <v>빙상부</v>
       </c>
       <c r="P50" t="str">
-        <v>시설관리처 시설기획부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q50" t="str">
         <v/>
@@ -3664,28 +3662,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-08-21 13:59:00</v>
+        <v>2026-08-21 17:09:00</v>
       </c>
       <c r="D51" t="str">
-        <v>양다혜</v>
+        <v>김민수</v>
       </c>
       <c r="E51" t="str">
         <v>행정6급</v>
       </c>
       <c r="F51" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G51" t="str">
-        <v>사업계획처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H51" t="str">
-        <v>판매·보상부</v>
+        <v>재무부</v>
       </c>
       <c r="I51" t="str">
-        <v>사업계획처 판매보상부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="J51" t="str">
         <v>지정제안</v>
@@ -3694,19 +3692,19 @@
         <v>지역상생</v>
       </c>
       <c r="L51" t="str">
-        <v>[지정제안] 시민회관 열린광장 프로젝트(공공공간 활용한 지역상생·민관협력형 생활문화공간 조성)</v>
+        <v>[지정제안] 원스톱 상생결제시스템 도입</v>
       </c>
       <c r="M51" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N51" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O51" t="str">
-        <v>여가체육부</v>
+        <v>재무부</v>
       </c>
       <c r="P51" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="Q51" t="str">
         <v/>
@@ -3729,49 +3727,49 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C52" t="str">
-        <v>2026-08-21 16:42:00</v>
+        <v>2026-08-23 13:20:00</v>
       </c>
       <c r="D52" t="str">
-        <v>최민기</v>
+        <v>한진욱</v>
       </c>
       <c r="E52" t="str">
-        <v>업무직</v>
+        <v>행정6급</v>
       </c>
       <c r="F52" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G52" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H52" t="str">
-        <v>빙상부</v>
+        <v>인사부</v>
       </c>
       <c r="I52" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="J52" t="str">
         <v>지정제안</v>
       </c>
       <c r="K52" t="str">
-        <v>안전</v>
+        <v>AI혁신</v>
       </c>
       <c r="L52" t="str">
-        <v>[지정제안] 지하 2층 빙상장 복도 화장실 앞 충돌방지(미끄럼방지 겸용) 스티커 부착</v>
+        <v>[지정제안] AI를 활용한 엑셀매크로기반 원클릭 업무체계 구축</v>
       </c>
       <c r="M52" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N52" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O52" t="str">
-        <v>빙상부</v>
+        <v>인사부</v>
       </c>
       <c r="P52" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="Q52" t="str">
         <v/>
@@ -3794,49 +3792,49 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-08-21 17:09:00</v>
+        <v>2026-08-24 16:16:00</v>
       </c>
       <c r="D53" t="str">
-        <v>김민수</v>
+        <v>곽용후</v>
       </c>
       <c r="E53" t="str">
-        <v>행정6급</v>
+        <v>체육7급</v>
       </c>
       <c r="F53" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G53" t="str">
-        <v>경영지원실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H53" t="str">
-        <v>재무부</v>
+        <v>볼링골프부</v>
       </c>
       <c r="I53" t="str">
-        <v>경영지원실 재무부</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="J53" t="str">
         <v>지정제안</v>
       </c>
       <c r="K53" t="str">
-        <v>지역상생</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L53" t="str">
-        <v>[지정제안] 원스톱 상생결제시스템 도입</v>
+        <v>[지정제안] 볼링 프로그램 추첨제 도입을 통한 수익 증대 및 운영 구조개선 방안</v>
       </c>
       <c r="M53" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N53" t="str">
-        <v>경영지원실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O53" t="str">
-        <v>재무부</v>
+        <v>볼링골프부</v>
       </c>
       <c r="P53" t="str">
-        <v>경영지원실 재무부</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="Q53" t="str">
         <v/>
@@ -3859,49 +3857,49 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C54" t="str">
-        <v>2026-08-23 13:20:00</v>
+        <v>2026-08-24 18:33:00</v>
       </c>
       <c r="D54" t="str">
-        <v>한진욱</v>
+        <v>김동규</v>
       </c>
       <c r="E54" t="str">
-        <v>행정6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F54" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G54" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="H54" t="str">
-        <v>인사부</v>
+        <v>시설운영부</v>
       </c>
       <c r="I54" t="str">
-        <v>경영지원실 인사부</v>
+        <v>시설운영부</v>
       </c>
       <c r="J54" t="str">
         <v>지정제안</v>
       </c>
       <c r="K54" t="str">
-        <v>AI혁신</v>
+        <v>안전사고 예방</v>
       </c>
       <c r="L54" t="str">
-        <v>[지정제안] AI를 활용한 엑셀매크로기반 원클릭 업무체계 구축</v>
+        <v>[지정제안] 시민회관 볼판 승강기 교체를 통한 안전사고 예방</v>
       </c>
       <c r="M54" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N54" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O54" t="str">
-        <v>인사부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P54" t="str">
-        <v>경영지원실 인사부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q54" t="str">
         <v/>
@@ -3924,16 +3922,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-08-24 15:56:00</v>
+        <v>2026-08-24 19:44:00</v>
       </c>
       <c r="D55" t="str">
-        <v>안경선</v>
+        <v>이정준</v>
       </c>
       <c r="E55" t="str">
-        <v>행정 4급</v>
+        <v>기술6급</v>
       </c>
       <c r="F55" t="str">
         <v>운영관리본부</v>
@@ -3942,19 +3940,19 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="H55" t="str">
-        <v>수련관운영부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I55" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J55" t="str">
-        <v>자유제안</v>
+        <v>지정제안</v>
       </c>
       <c r="K55" t="str">
         <v>안전</v>
       </c>
       <c r="L55" t="str">
-        <v>(자유제안) 화장실 위생 개선 및 노로바이러스 감염 예방을 위한 양변기 손잡이 설치</v>
+        <v>[지정제안] 친환경 태양광 스마트벤치 도입을 통한 공원 내 야간 안전 강화 및 시민 편의 혁신</v>
       </c>
       <c r="M55" t="str">
         <v>운영관리본부</v>
@@ -3969,20 +3967,20 @@
         <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q55" t="str">
-        <v>중복</v>
+        <v>보류(채택결과 미확인)</v>
       </c>
       <c r="R55" t="str">
-        <v/>
+        <v>2023-10-082 태양광 스마트 벤치 설치</v>
       </c>
       <c r="S55" t="str">
-        <v>중복 가능성 높음(채택)</v>
+        <v>판단보류(채택결과 미확인)</v>
       </c>
       <c r="T55" t="str" xml:space="preserve">
-        <v xml:space="preserve">2021-04-020 개인위생 강화를 위한 화장실 변기뚜껑 손잡이 설치(코로나19 확산방지)_x000d_
-심사결과: 채택 [2022년 제안!G20]</v>
+        <v xml:space="preserve">2023-10-082 태양광 스마트 벤치 설치_x000d_
+채택결과 확인 불가 [제안 본문에 심사결과 없음]</v>
       </c>
       <c r="U55" t="str">
-        <v>2021-04-020은 심사결과 채택으로 확인됨. 변기 뚜껑에 손잡이를 부착하여 직접 접촉을 줄이고 위생을 개선하는 핵심 수단·목적이 이번 제안과 같음. 2024-07-117은 부적합이므로 중복 판단 근거에서 제외함. 항균 소재·안내 스티커 추가의 차별성은 별도 검토 필요.</v>
+        <v>기존 중복 표시를 재검토함. 태양광 벤치의 조명·충전 기능과 설치 공원은 겹치지만 과거 제안의 채택결과가 자료에 없음. 기존 중복 표시는 채택결과 확인 전 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
       </c>
     </row>
     <row r="56">
@@ -3990,49 +3988,49 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C56" t="str">
-        <v>2026-08-24 16:16:00</v>
+        <v>2026-08-24 20:22:00</v>
       </c>
       <c r="D56" t="str">
-        <v>곽용후</v>
+        <v>이정준</v>
       </c>
       <c r="E56" t="str">
-        <v>체육7급</v>
+        <v>기술6급</v>
       </c>
       <c r="F56" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G56" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H56" t="str">
-        <v>볼링골프부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I56" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J56" t="str">
         <v>지정제안</v>
       </c>
       <c r="K56" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>업무개선</v>
       </c>
       <c r="L56" t="str">
-        <v>[지정제안] 볼링 프로그램 추첨제 도입을 통한 수익 증대 및 운영 구조개선 방안</v>
+        <v>[지정제안] 드론 도입을 통한 시설 예방관리 강화 및 개선 방안</v>
       </c>
       <c r="M56" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N56" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O56" t="str">
-        <v>볼링골프부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P56" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q56" t="str">
         <v/>
@@ -4055,49 +4053,49 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-08-24 18:33:00</v>
+        <v>2026-08-25 11:17:00</v>
       </c>
       <c r="D57" t="str">
-        <v>김동규</v>
+        <v>신동진</v>
       </c>
       <c r="E57" t="str">
         <v>기술6급</v>
       </c>
       <c r="F57" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="G57" t="str">
-        <v>시설관리처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="H57" t="str">
-        <v>시설운영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="I57" t="str">
-        <v>시설운영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="J57" t="str">
         <v>지정제안</v>
       </c>
       <c r="K57" t="str">
-        <v>안전사고 예방</v>
+        <v>안전</v>
       </c>
       <c r="L57" t="str">
-        <v>[지정제안] 시민회관 볼판 승강기 교체를 통한 안전사고 예방</v>
+        <v>[지정제안]안전사고 발굴 및 시설물 개선 필요사항 제안 체계 구축을 통한 사전 안전사고 예방</v>
       </c>
       <c r="M57" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N57" t="str">
-        <v>시설관리처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O57" t="str">
-        <v>시설운영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P57" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q57" t="str">
         <v/>
@@ -4120,28 +4118,28 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C58" t="str">
-        <v>2026-08-24 19:44:00</v>
+        <v>2026-08-25 14:53:00</v>
       </c>
       <c r="D58" t="str">
-        <v>이정준</v>
+        <v>이민호</v>
       </c>
       <c r="E58" t="str">
-        <v>기술6급</v>
+        <v>업무직(사무기술)</v>
       </c>
       <c r="F58" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G58" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H58" t="str">
-        <v>시설지원부</v>
+        <v>볼링골프부</v>
       </c>
       <c r="I58" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="J58" t="str">
         <v>지정제안</v>
@@ -4150,35 +4148,35 @@
         <v>안전</v>
       </c>
       <c r="L58" t="str">
-        <v>[지정제안] 친환경 태양광 스마트벤치 도입을 통한 공원 내 야간 안전 강화 및 시민 편의 혁신</v>
+        <v>[지정제안] 골프장 안전사고 방지용 보호대 설치</v>
       </c>
       <c r="M58" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N58" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O58" t="str">
-        <v>시설지원부</v>
+        <v>볼링골프부</v>
       </c>
       <c r="P58" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="Q58" t="str">
-        <v>보류(채택결과 미확인)</v>
+        <v/>
       </c>
       <c r="R58" t="str">
-        <v>2023-10-082 태양광 스마트 벤치 설치</v>
+        <v/>
       </c>
       <c r="S58" t="str">
-        <v>판단보류(채택결과 미확인)</v>
+        <v>유사(채택)</v>
       </c>
       <c r="T58" t="str" xml:space="preserve">
-        <v xml:space="preserve">2023-10-082 태양광 스마트 벤치 설치_x000d_
-채택결과 확인 불가 [제안 본문에 심사결과 없음]</v>
+        <v xml:space="preserve">2025-10-140 골프연습장 안전사고 예방을 위한 타석 간 그물망 설치_x000d_
+심사결과: 채택 [2025년 제안 총괄 !I129]</v>
       </c>
       <c r="U58" t="str">
-        <v>기존 중복 표시를 재검토함. 태양광 벤치의 조명·충전 기능과 설치 공원은 겹치지만 과거 제안의 채택결과가 자료에 없음. 기존 중복 표시는 채택결과 확인 전 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
+        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 골프연습장 타석 간 그물망을 설치하여 안전사고를 방지하는 제안임. 이번도 인접 타석으로 공이 유입되거나 튕겨 나오는 것을 막는 보호대 설치로 대상·목적이 겹침. 기존 본문은 붙임 참조이므로 그물망과 이번 보호대의 구조·차단 구간을 대조해야 함.</v>
       </c>
     </row>
     <row r="59">
@@ -4186,49 +4184,49 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-08-24 20:22:00</v>
+        <v>2026-08-25 15:14:00</v>
       </c>
       <c r="D59" t="str">
-        <v>이정준</v>
+        <v>변세진</v>
       </c>
       <c r="E59" t="str">
-        <v>기술6급</v>
+        <v>체육6급</v>
       </c>
       <c r="F59" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G59" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H59" t="str">
-        <v>시설지원부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I59" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="J59" t="str">
         <v>지정제안</v>
       </c>
       <c r="K59" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L59" t="str">
-        <v>[지정제안] 드론 도입을 통한 시설 예방관리 강화 및 개선 방안</v>
+        <v>[지정제안] 상상하랑 어린이 프로그램 안심인계 호출벨 설치·운영</v>
       </c>
       <c r="M59" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N59" t="str">
-        <v>공원수련관관리처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O59" t="str">
-        <v>시설지원부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P59" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q59" t="str">
         <v/>
@@ -4251,28 +4249,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-08-25 11:17:00</v>
+        <v>2026-08-25 15:48:00</v>
       </c>
       <c r="D60" t="str">
-        <v>신동진</v>
+        <v>김범석</v>
       </c>
       <c r="E60" t="str">
-        <v>기술6급</v>
+        <v>체육4급</v>
       </c>
       <c r="F60" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G60" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H60" t="str">
-        <v>안전총괄단</v>
+        <v>볼링골프부</v>
       </c>
       <c r="I60" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="J60" t="str">
         <v>지정제안</v>
@@ -4281,19 +4279,19 @@
         <v>안전</v>
       </c>
       <c r="L60" t="str">
-        <v>[지정제안]안전사고 발굴 및 시설물 개선 필요사항 제안 체계 구축을 통한 사전 안전사고 예방</v>
+        <v>안전사고 예방을 위한 볼링장 산업안전보건협의체 운영</v>
       </c>
       <c r="M60" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N60" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O60" t="str">
-        <v>안전총괄단</v>
+        <v>볼링골프부</v>
       </c>
       <c r="P60" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처 볼링골프부</v>
       </c>
       <c r="Q60" t="str">
         <v/>
@@ -4311,54 +4309,54 @@
         <v/>
       </c>
     </row>
-    <row r="61" xml:space="preserve">
+    <row r="61">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-08-25 14:53:00</v>
+        <v>2026-08-25 15:48:00</v>
       </c>
       <c r="D61" t="str">
-        <v>이민호</v>
+        <v>한진숙</v>
       </c>
       <c r="E61" t="str">
-        <v>업무직(사무기술)</v>
+        <v>행정6급</v>
       </c>
       <c r="F61" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G61" t="str">
-        <v>시민회관체육운영처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H61" t="str">
-        <v>볼링골프부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I61" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>사업계획처 판매보상부</v>
       </c>
       <c r="J61" t="str">
         <v>지정제안</v>
       </c>
       <c r="K61" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L61" t="str">
-        <v>[지정제안] 골프장 안전사고 방지용 보호대 설치</v>
+        <v>[지정제안]일반민원 3일 일괄 처리기준을 민원 유형별 처리기간으로 개선</v>
       </c>
       <c r="M61" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N61" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O61" t="str">
-        <v>볼링골프부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P61" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q61" t="str">
         <v/>
@@ -4367,14 +4365,13 @@
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T61" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-10-140 골프연습장 안전사고 예방을 위한 타석 간 그물망 설치_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I129]</v>
+        <v/>
+      </c>
+      <c r="T61" t="str">
+        <v/>
       </c>
       <c r="U61" t="str">
-        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 골프연습장 타석 간 그물망을 설치하여 안전사고를 방지하는 제안임. 이번도 인접 타석으로 공이 유입되거나 튕겨 나오는 것을 막는 보호대 설치로 대상·목적이 겹침. 기존 본문은 붙임 참조이므로 그물망과 이번 보호대의 구조·차단 구간을 대조해야 함.</v>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -4382,16 +4379,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-08-25 15:14:00</v>
+        <v>2026-08-25 15:54:00</v>
       </c>
       <c r="D62" t="str">
-        <v>변세진</v>
+        <v>김민규</v>
       </c>
       <c r="E62" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F62" t="str">
         <v>운영관리본부</v>
@@ -4400,31 +4397,31 @@
         <v>시민회관체육운영처</v>
       </c>
       <c r="H62" t="str">
-        <v>여가체육부</v>
+        <v>빙상부</v>
       </c>
       <c r="I62" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
+        <v>체육운영처 빙상부</v>
       </c>
       <c r="J62" t="str">
         <v>지정제안</v>
       </c>
       <c r="K62" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L62" t="str">
-        <v>[지정제안] 상상하랑 어린이 프로그램 안심인계 호출벨 설치·운영</v>
+        <v>(지정제안) 빙상장 피겨 강습 출입시 안내 문구 현수막</v>
       </c>
       <c r="M62" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N62" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O62" t="str">
-        <v>안전총괄단</v>
+        <v>빙상부</v>
       </c>
       <c r="P62" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q62" t="str">
         <v/>
@@ -4447,16 +4444,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-08-25 15:48:00</v>
+        <v>2026-08-25 17:52:00</v>
       </c>
       <c r="D63" t="str">
-        <v>김범석</v>
+        <v>윤지혜</v>
       </c>
       <c r="E63" t="str">
-        <v>체육4급</v>
+        <v>체육6급</v>
       </c>
       <c r="F63" t="str">
         <v>운영관리본부</v>
@@ -4465,10 +4462,10 @@
         <v>시민회관체육운영처</v>
       </c>
       <c r="H63" t="str">
-        <v>볼링골프부</v>
+        <v>빙상부</v>
       </c>
       <c r="I63" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J63" t="str">
         <v>지정제안</v>
@@ -4477,19 +4474,19 @@
         <v>안전</v>
       </c>
       <c r="L63" t="str">
-        <v>안전사고 예방을 위한 볼링장 산업안전보건협의체 운영</v>
+        <v>과천 AI시민안전 파트너</v>
       </c>
       <c r="M63" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N63" t="str">
-        <v>시민회관체육운영처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O63" t="str">
-        <v>볼링골프부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P63" t="str">
-        <v>시민회관체육운영처 볼링골프부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q63" t="str">
         <v/>
@@ -4512,49 +4509,49 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-08-25 15:48:00</v>
+        <v>2026-08-26 09:24:00</v>
       </c>
       <c r="D64" t="str">
-        <v>한진숙</v>
+        <v>성화진</v>
       </c>
       <c r="E64" t="str">
-        <v>행정6급</v>
+        <v>기술 6급</v>
       </c>
       <c r="F64" t="str">
-        <v>개발사업본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="G64" t="str">
-        <v>사업계획처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="H64" t="str">
-        <v>판매·보상부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="I64" t="str">
-        <v>사업계획처 판매보상부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="J64" t="str">
         <v>지정제안</v>
       </c>
       <c r="K64" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L64" t="str">
-        <v>[지정제안]일반민원 3일 일괄 처리기준을 민원 유형별 처리기간으로 개선</v>
+        <v>(지정제안) 운동 전 10초! 자가안전확인제 운영</v>
       </c>
       <c r="M64" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N64" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O64" t="str">
-        <v>총무행정부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P64" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q64" t="str">
         <v/>
@@ -4577,49 +4574,49 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-08-25 15:54:00</v>
+        <v>2026-08-26 09:33:00</v>
       </c>
       <c r="D65" t="str">
-        <v>김민규</v>
+        <v>김다정</v>
       </c>
       <c r="E65" t="str">
-        <v>기술6급</v>
+        <v>행정5급</v>
       </c>
       <c r="F65" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G65" t="str">
-        <v>시민회관체육운영처</v>
+        <v>미래전략실</v>
       </c>
       <c r="H65" t="str">
-        <v>빙상부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="I65" t="str">
-        <v>체육운영처 빙상부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="J65" t="str">
         <v>지정제안</v>
       </c>
       <c r="K65" t="str">
-        <v>업무개선</v>
+        <v>AI혁신</v>
       </c>
       <c r="L65" t="str">
-        <v>(지정제안) 빙상장 피겨 강습 출입시 안내 문구 현수막</v>
+        <v>스마트 벤치마킹 AI 비서: 타 기관 우수사례 자동 분석 시스템</v>
       </c>
       <c r="M65" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N65" t="str">
-        <v>시민회관체육운영처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O65" t="str">
-        <v>빙상부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="P65" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="Q65" t="str">
         <v/>
@@ -4642,16 +4639,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-08-25 17:52:00</v>
+        <v>2026-08-26 10:24:00</v>
       </c>
       <c r="D66" t="str">
-        <v>윤지혜</v>
+        <v>박선경</v>
       </c>
       <c r="E66" t="str">
-        <v>체육6급</v>
+        <v>업무직</v>
       </c>
       <c r="F66" t="str">
         <v>운영관리본부</v>
@@ -4666,25 +4663,25 @@
         <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J66" t="str">
-        <v>지정제안</v>
+        <v>실행제안</v>
       </c>
       <c r="K66" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L66" t="str">
-        <v>과천 AI시민안전 파트너</v>
+        <v>[실행제안]과천시민회관 빙상장 시재금 축소</v>
       </c>
       <c r="M66" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N66" t="str">
-        <v>시설관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O66" t="str">
-        <v>시설운영부</v>
+        <v>빙상부</v>
       </c>
       <c r="P66" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q66" t="str">
         <v/>
@@ -4707,37 +4704,37 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C67" t="str">
-        <v>2026-08-26 09:24:00</v>
+        <v>2026-08-26 10:46:00</v>
       </c>
       <c r="D67" t="str">
-        <v>성화진</v>
+        <v>이은석</v>
       </c>
       <c r="E67" t="str">
-        <v>기술 6급</v>
+        <v>기술4급</v>
       </c>
       <c r="F67" t="str">
-        <v>사장 직속</v>
+        <v>경영부문</v>
       </c>
       <c r="G67" t="str">
-        <v>안전총괄단</v>
+        <v>미래전략실</v>
       </c>
       <c r="H67" t="str">
-        <v>안전총괄단</v>
+        <v>스마트정보부</v>
       </c>
       <c r="I67" t="str">
-        <v>안전총괄단</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="J67" t="str">
         <v>지정제안</v>
       </c>
       <c r="K67" t="str">
-        <v>안전</v>
+        <v>AI혁신</v>
       </c>
       <c r="L67" t="str">
-        <v>(지정제안) 운동 전 10초! 자가안전확인제 운영</v>
+        <v>AX 대전환 시범사업 추진 : 공공시설 AI청소로봇 도입</v>
       </c>
       <c r="M67" t="str">
         <v>운영관리본부</v>
@@ -4772,49 +4769,49 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-08-26 09:33:00</v>
+        <v>2026-08-26 13:36:00</v>
       </c>
       <c r="D68" t="str">
-        <v>김다정</v>
+        <v>김성희</v>
       </c>
       <c r="E68" t="str">
-        <v>행정5급</v>
+        <v>행정6급</v>
       </c>
       <c r="F68" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G68" t="str">
-        <v>미래전략실</v>
+        <v>시설관리처</v>
       </c>
       <c r="H68" t="str">
-        <v>미래혁신부</v>
+        <v>주차관리부</v>
       </c>
       <c r="I68" t="str">
-        <v>미래전략실 미래혁신부</v>
+        <v>시설관리처 추차관리부</v>
       </c>
       <c r="J68" t="str">
         <v>지정제안</v>
       </c>
       <c r="K68" t="str">
-        <v>AI혁신</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L68" t="str">
-        <v>스마트 벤치마킹 AI 비서: 타 기관 우수사례 자동 분석 시스템</v>
+        <v>QR코드를 활용한 공영주차장(유인) 모바일 사전정산 도입</v>
       </c>
       <c r="M68" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N68" t="str">
-        <v>미래전략실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O68" t="str">
-        <v>미래혁신부</v>
+        <v>주차관리부</v>
       </c>
       <c r="P68" t="str">
-        <v>미래전략실 미래혁신부</v>
+        <v>시설관리처 주차관리부</v>
       </c>
       <c r="Q68" t="str">
         <v/>
@@ -4837,49 +4834,49 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C69" t="str">
-        <v>2026-08-26 10:24:00</v>
+        <v>2026-08-26 13:42:00</v>
       </c>
       <c r="D69" t="str">
-        <v>박선경</v>
+        <v>우한솔</v>
       </c>
       <c r="E69" t="str">
-        <v>업무직</v>
+        <v>행정7급</v>
       </c>
       <c r="F69" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G69" t="str">
-        <v>시민회관체육운영처</v>
+        <v>미래전략실</v>
       </c>
       <c r="H69" t="str">
-        <v>빙상부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="I69" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="J69" t="str">
-        <v>실행제안</v>
+        <v>지정제안</v>
       </c>
       <c r="K69" t="str">
         <v>업무개선</v>
       </c>
       <c r="L69" t="str">
-        <v>[실행제안]과천시민회관 빙상장 시재금 축소</v>
+        <v>AI 기반 지방공기업 동향 모니터링 대시보드</v>
       </c>
       <c r="M69" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N69" t="str">
-        <v>시민회관체육운영처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O69" t="str">
-        <v>빙상부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="P69" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="Q69" t="str">
         <v/>
@@ -4897,54 +4894,54 @@
         <v/>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-08-26 10:46:00</v>
+        <v>2026-08-26 13:57:00</v>
       </c>
       <c r="D70" t="str">
-        <v>이은석</v>
+        <v>오세풍</v>
       </c>
       <c r="E70" t="str">
-        <v>기술4급</v>
+        <v>체육 5급</v>
       </c>
       <c r="F70" t="str">
-        <v>경영부문</v>
+        <v>사장 직속</v>
       </c>
       <c r="G70" t="str">
-        <v>미래전략실</v>
+        <v>안전총괄단</v>
       </c>
       <c r="H70" t="str">
-        <v>스마트정보부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="I70" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="J70" t="str">
         <v>지정제안</v>
       </c>
       <c r="K70" t="str">
-        <v>AI혁신</v>
+        <v>안전</v>
       </c>
       <c r="L70" t="str">
-        <v>AX 대전환 시범사업 추진 : 공공시설 AI청소로봇 도입</v>
+        <v>(지정제안) 야외 체육시설 소화기 및 옥외 소화기함 설치 운영</v>
       </c>
       <c r="M70" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N70" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O70" t="str">
-        <v>시설운영부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P70" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q70" t="str">
         <v/>
@@ -4953,13 +4950,14 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v/>
-      </c>
-      <c r="T70" t="str">
-        <v/>
+        <v>유사(채택)</v>
+      </c>
+      <c r="T70" t="str" xml:space="preserve">
+        <v xml:space="preserve">2025-10-191 시민 안심 잔디마당, 초기 대응 강화를 위한 옥외 소화기 설치_x000d_
+심사결과: 채택 [2025년 제안 총괄 !I174]</v>
       </c>
       <c r="U70" t="str">
-        <v/>
+        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 잔디마당에 옥외 소화기·보관함·위치 표지를 설치하고 정기점검하는 제안임. 이번은 관문·문원·갈현 야외 체육시설에 소화기·밀폐형 보호함·축광 표지를 설치하는 방식으로 수단은 같고 적용 시설이 확대됨. 시설 차이만으로 신규성이 인정되는지 검토 필요.</v>
       </c>
     </row>
     <row r="71">
@@ -4967,49 +4965,49 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-08-26 13:36:00</v>
+        <v>2026-08-26 17:40:00</v>
       </c>
       <c r="D71" t="str">
-        <v>김성희</v>
+        <v>장소희</v>
       </c>
       <c r="E71" t="str">
-        <v>행정6급</v>
+        <v>체육4급</v>
       </c>
       <c r="F71" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G71" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H71" t="str">
-        <v>주차관리부</v>
+        <v>공원운영부</v>
       </c>
       <c r="I71" t="str">
-        <v>시설관리처 추차관리부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="J71" t="str">
         <v>지정제안</v>
       </c>
       <c r="K71" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>고객서비스</v>
       </c>
       <c r="L71" t="str">
-        <v>QR코드를 활용한 공영주차장(유인) 모바일 사전정산 도입</v>
+        <v>생성형 AI를 활용한 체육공원 시설 안내도 제작 및 이용정보 개선</v>
       </c>
       <c r="M71" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N71" t="str">
-        <v>시설관리처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O71" t="str">
-        <v>주차관리부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P71" t="str">
-        <v>시설관리처 주차관리부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q71" t="str">
         <v/>
@@ -5032,16 +5030,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-08-26 13:42:00</v>
+        <v>2026-08-26 17:57:00</v>
       </c>
       <c r="D72" t="str">
-        <v>우한솔</v>
+        <v>이정민</v>
       </c>
       <c r="E72" t="str">
-        <v>행정7급</v>
+        <v>행정4급</v>
       </c>
       <c r="F72" t="str">
         <v>경영부문</v>
@@ -5059,10 +5057,10 @@
         <v>지정제안</v>
       </c>
       <c r="K72" t="str">
-        <v>업무개선</v>
+        <v>제도개선</v>
       </c>
       <c r="L72" t="str">
-        <v>AI 기반 지방공기업 동향 모니터링 대시보드</v>
+        <v>신규사업 운영기준 수립을 통한 사업성·리스크 사전관리체계 구축</v>
       </c>
       <c r="M72" t="str">
         <v>경영부문</v>
@@ -5097,28 +5095,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-08-26 13:57:00</v>
+        <v>2026-08-26 19:20:00</v>
       </c>
       <c r="D73" t="str">
-        <v>오세풍</v>
+        <v>김승현</v>
       </c>
       <c r="E73" t="str">
-        <v>체육 5급</v>
+        <v>체육7급</v>
       </c>
       <c r="F73" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G73" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H73" t="str">
-        <v>안전총괄단</v>
+        <v>수련관운영부</v>
       </c>
       <c r="I73" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="J73" t="str">
         <v>지정제안</v>
@@ -5127,7 +5125,7 @@
         <v>안전</v>
       </c>
       <c r="L73" t="str">
-        <v>(지정제안) 야외 체육시설 소화기 및 옥외 소화기함 설치 운영</v>
+        <v>화재 대응 능력 강화를 위한 부착형 소화패치 도입</v>
       </c>
       <c r="M73" t="str">
         <v>운영관리본부</v>
@@ -5136,276 +5134,276 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="O73" t="str">
-        <v>공원운영부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="P73" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="Q73" t="str">
-        <v/>
-      </c>
-      <c r="R73" t="str">
-        <v/>
-      </c>
-      <c r="S73" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T73" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-10-191 시민 안심 잔디마당, 초기 대응 강화를 위한 옥외 소화기 설치_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I174]</v>
-      </c>
-      <c r="U73" t="str">
-        <v>과거 심사결과가 채택인 비교안에 한해 검토함. 기존은 잔디마당에 옥외 소화기·보관함·위치 표지를 설치하고 정기점검하는 제안임. 이번은 관문·문원·갈현 야외 체육시설에 소화기·밀폐형 보호함·축광 표지를 설치하는 방식으로 수단은 같고 적용 시설이 확대됨. 시설 차이만으로 신규성이 인정되는지 검토 필요.</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>82</v>
-      </c>
-      <c r="C74" t="str">
-        <v>2026-08-26 17:40:00</v>
-      </c>
-      <c r="D74" t="str">
-        <v>장소희</v>
-      </c>
-      <c r="E74" t="str">
-        <v>체육4급</v>
-      </c>
-      <c r="F74" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G74" t="str">
-        <v>공원수련관관리처</v>
-      </c>
-      <c r="H74" t="str">
-        <v>공원운영부</v>
-      </c>
-      <c r="I74" t="str">
-        <v>공원수련관관리처 공원운영부</v>
-      </c>
-      <c r="J74" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K74" t="str">
-        <v>고객서비스</v>
-      </c>
-      <c r="L74" t="str">
-        <v>생성형 AI를 활용한 체육공원 시설 안내도 제작 및 이용정보 개선</v>
-      </c>
-      <c r="M74" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N74" t="str">
-        <v>공원수련관관리처</v>
-      </c>
-      <c r="O74" t="str">
-        <v>공원운영부</v>
-      </c>
-      <c r="P74" t="str">
-        <v>공원수련관관리처 공원운영부</v>
-      </c>
-      <c r="Q74" t="str">
-        <v/>
-      </c>
-      <c r="R74" t="str">
-        <v/>
-      </c>
-      <c r="S74" t="str">
-        <v/>
-      </c>
-      <c r="T74" t="str">
-        <v/>
-      </c>
-      <c r="U74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>83</v>
-      </c>
-      <c r="C75" t="str">
-        <v>2026-08-26 17:57:00</v>
-      </c>
-      <c r="D75" t="str">
-        <v>이정민</v>
-      </c>
-      <c r="E75" t="str">
-        <v>행정4급</v>
-      </c>
-      <c r="F75" t="str">
-        <v>경영부문</v>
-      </c>
-      <c r="G75" t="str">
-        <v>미래전략실</v>
-      </c>
-      <c r="H75" t="str">
-        <v>미래혁신부</v>
-      </c>
-      <c r="I75" t="str">
-        <v>미래전략실 미래혁신부</v>
-      </c>
-      <c r="J75" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K75" t="str">
-        <v>제도개선</v>
-      </c>
-      <c r="L75" t="str">
-        <v>신규사업 운영기준 수립을 통한 사업성·리스크 사전관리체계 구축</v>
-      </c>
-      <c r="M75" t="str">
-        <v>경영부문</v>
-      </c>
-      <c r="N75" t="str">
-        <v>미래전략실</v>
-      </c>
-      <c r="O75" t="str">
-        <v>미래혁신부</v>
-      </c>
-      <c r="P75" t="str">
-        <v>미래전략실 미래혁신부</v>
-      </c>
-      <c r="Q75" t="str">
-        <v/>
-      </c>
-      <c r="R75" t="str">
-        <v/>
-      </c>
-      <c r="S75" t="str">
-        <v/>
-      </c>
-      <c r="T75" t="str">
-        <v/>
-      </c>
-      <c r="U75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>84</v>
-      </c>
-      <c r="C76" t="str">
-        <v>2026-08-26 19:20:00</v>
-      </c>
-      <c r="D76" t="str">
-        <v>김승현</v>
-      </c>
-      <c r="E76" t="str">
-        <v>체육7급</v>
-      </c>
-      <c r="F76" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G76" t="str">
-        <v>공원수련관관리처</v>
-      </c>
-      <c r="H76" t="str">
-        <v>수련관운영부</v>
-      </c>
-      <c r="I76" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
-      </c>
-      <c r="J76" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K76" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L76" t="str">
-        <v>화재 대응 능력 강화를 위한 부착형 소화패치 도입</v>
-      </c>
-      <c r="M76" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N76" t="str">
-        <v>공원수련관관리처</v>
-      </c>
-      <c r="O76" t="str">
-        <v>수련관운영부</v>
-      </c>
-      <c r="P76" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
-      </c>
-      <c r="Q76" t="str">
         <v>보류(채택결과 미확인)</v>
       </c>
-      <c r="R76" t="str" xml:space="preserve">
+      <c r="R73" t="str" xml:space="preserve">
         <v xml:space="preserve">2024-12-277 자동소화 패치 도입을 통한 전기 화재 예방_x000d_
 2022-12-197 소화패치(혁신제품) 활용으로 실내 화재방지(화재 초기 대응)</v>
       </c>
-      <c r="S76" t="str">
+      <c r="S73" t="str">
         <v>판단보류(채택결과 미확인)</v>
       </c>
-      <c r="T76" t="str" xml:space="preserve">
+      <c r="T73" t="str" xml:space="preserve">
         <v xml:space="preserve">2022-12-197 소화패치(혁신제품) 활용으로 실내 화재방지(화재 초기 대응)_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]_x000d_
 _x000d_
 2024-12-277 자동소화 패치 도입을 통한 전기 화재 예방_x000d_
 심사결과: 부적합 [2024년 제안!I141]</v>
       </c>
+      <c r="U73" t="str">
+        <v>기존 중복 표시를 재검토함. 2024-12-277은 부적합으로 채택안이 아니며, 2022-12-197은 본문만 있고 채택결과를 확인할 수 없음. 소화패치의 내용이 겹치더라도 채택 근거 확보 전에는 중복으로 확정할 수 없음. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>85</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2026-08-27 06:40:00</v>
+      </c>
+      <c r="D74" t="str">
+        <v>김상현</v>
+      </c>
+      <c r="E74" t="str">
+        <v>업무직</v>
+      </c>
+      <c r="F74" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G74" t="str">
+        <v>시민회관체육운영처</v>
+      </c>
+      <c r="H74" t="str">
+        <v>빙상부</v>
+      </c>
+      <c r="I74" t="str">
+        <v>시민회관체육운영처 빙상부</v>
+      </c>
+      <c r="J74" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K74" t="str">
+        <v>안전</v>
+      </c>
+      <c r="L74" t="str">
+        <v>[지정제안] 영상미디어(QR코드)를 활용한 안전사고 예방</v>
+      </c>
+      <c r="M74" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N74" t="str">
+        <v>시민회관체육운영처</v>
+      </c>
+      <c r="O74" t="str">
+        <v>빙상부</v>
+      </c>
+      <c r="P74" t="str">
+        <v>시민회관체육운영처 빙상부</v>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v>유사(채택)</v>
+      </c>
+      <c r="T74" t="str" xml:space="preserve">
+        <v xml:space="preserve">빙상장 안전수칙 및 벌클스케이트 사용방법 QR코드 제작 사용_x000d_
+심사결과: 채택 [2021년 제안!I78, 연번 75]</v>
+      </c>
+      <c r="U74" t="str">
+        <v>2021년 제안 시트 78행의 QR 안전수칙·버클스케이트 사용방법 제안은 심사결과 채택임. 안내내용·QR 전달수단은 겹치지만 이번은 영상과 대여 전 시청완료 확인을 추가함. 2025-10-124는 불채택&gt;50(40점)이므로 채택 근거에서 제외함.</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>86</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2026-08-27 09:36:00</v>
+      </c>
+      <c r="D75" t="str">
+        <v>김만전</v>
+      </c>
+      <c r="E75" t="str">
+        <v>기술4급</v>
+      </c>
+      <c r="F75" t="str">
+        <v>사장 직속</v>
+      </c>
+      <c r="G75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="H75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="I75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="J75" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K75" t="str">
+        <v>안전</v>
+      </c>
+      <c r="L75" t="str">
+        <v>시설이용 고객을 위한 안전수칙 제작 및 게시</v>
+      </c>
+      <c r="M75" t="str">
+        <v>사장 직속</v>
+      </c>
+      <c r="N75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="O75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="P75" t="str">
+        <v>안전총괄단</v>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
+      <c r="U75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>88</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2026-08-27 11:36:00</v>
+      </c>
+      <c r="D76" t="str">
+        <v>오준영</v>
+      </c>
+      <c r="E76" t="str">
+        <v>기술7급</v>
+      </c>
+      <c r="F76" t="str">
+        <v>경영부문</v>
+      </c>
+      <c r="G76" t="str">
+        <v>미래전략실</v>
+      </c>
+      <c r="H76" t="str">
+        <v>스마트정보부</v>
+      </c>
+      <c r="I76" t="str">
+        <v>미래전략실 스마트정보부</v>
+      </c>
+      <c r="J76" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K76" t="str">
+        <v>제도개선</v>
+      </c>
+      <c r="L76" t="str">
+        <v>[지정제안] 오픈소스 기반 전자서명 솔루션 구축</v>
+      </c>
+      <c r="M76" t="str">
+        <v>경영부문</v>
+      </c>
+      <c r="N76" t="str">
+        <v>미래전략실</v>
+      </c>
+      <c r="O76" t="str">
+        <v>스마트정보부</v>
+      </c>
+      <c r="P76" t="str">
+        <v>미래전략실 스마트정보부</v>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
       <c r="U76" t="str">
-        <v>기존 중복 표시를 재검토함. 2024-12-277은 부적합으로 채택안이 아니며, 2022-12-197은 본문만 있고 채택결과를 확인할 수 없음. 소화패치의 내용이 겹치더라도 채택 근거 확보 전에는 중복으로 확정할 수 없음. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
-      </c>
-    </row>
-    <row r="77" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C77" t="str">
-        <v>2026-08-27 06:40:00</v>
+        <v>2026-08-27 13:16:00</v>
       </c>
       <c r="D77" t="str">
-        <v>김상현</v>
+        <v>장소희</v>
       </c>
       <c r="E77" t="str">
-        <v>업무직</v>
+        <v>체육4급</v>
       </c>
       <c r="F77" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G77" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H77" t="str">
-        <v>빙상부</v>
+        <v>공원운영부</v>
       </c>
       <c r="I77" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="J77" t="str">
         <v>지정제안</v>
       </c>
       <c r="K77" t="str">
-        <v>안전</v>
+        <v>예산절감(수익창출)</v>
       </c>
       <c r="L77" t="str">
-        <v>[지정제안] 영상미디어(QR코드)를 활용한 안전사고 예방</v>
+        <v>[지정제안] 안내데스크 탄력적 무인운영을 통한 인건비 절감 및 수익구조 개선</v>
       </c>
       <c r="M77" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N77" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O77" t="str">
-        <v>빙상부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P77" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q77" t="str">
         <v/>
@@ -5414,14 +5412,13 @@
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T77" t="str" xml:space="preserve">
-        <v xml:space="preserve">빙상장 안전수칙 및 벌클스케이트 사용방법 QR코드 제작 사용_x000d_
-심사결과: 채택 [2021년 제안!I78, 연번 75]</v>
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
       </c>
       <c r="U77" t="str">
-        <v>2021년 제안 시트 78행의 QR 안전수칙·버클스케이트 사용방법 제안은 심사결과 채택임. 안내내용·QR 전달수단은 겹치지만 이번은 영상과 대여 전 시청완료 확인을 추가함. 2025-10-124는 불채택&gt;50(40점)이므로 채택 근거에서 제외함.</v>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -5429,49 +5426,49 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C78" t="str">
-        <v>2026-08-27 09:36:00</v>
+        <v>2026-08-27 14:34:00</v>
       </c>
       <c r="D78" t="str">
-        <v>김만전</v>
+        <v>박병진</v>
       </c>
       <c r="E78" t="str">
-        <v>기술4급</v>
+        <v>행정7급(기간제)</v>
       </c>
       <c r="F78" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G78" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H78" t="str">
-        <v>안전총괄단</v>
+        <v>공원운영부</v>
       </c>
       <c r="I78" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="J78" t="str">
         <v>지정제안</v>
       </c>
       <c r="K78" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L78" t="str">
-        <v>시설이용 고객을 위한 안전수칙 제작 및 게시</v>
+        <v>[지정제안] 전산·전력 마비 상황 대비 안내데스크 비상 운영 키트 배치</v>
       </c>
       <c r="M78" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N78" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O78" t="str">
-        <v>안전총괄단</v>
+        <v>공원운영부</v>
       </c>
       <c r="P78" t="str">
-        <v>안전총괄단</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q78" t="str">
         <v/>
@@ -5489,70 +5486,69 @@
         <v/>
       </c>
     </row>
-    <row r="79" xml:space="preserve">
+    <row r="79">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C79" t="str">
-        <v>2026-08-27 10:16:00</v>
+        <v>2026-08-27 15:26:00</v>
       </c>
       <c r="D79" t="str">
-        <v>선우효</v>
+        <v>안경선</v>
       </c>
       <c r="E79" t="str">
-        <v>업무직</v>
+        <v>행정 4급</v>
       </c>
       <c r="F79" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G79" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H79" t="str">
-        <v>빙상부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="I79" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>공원수련관관리처 수련관운영부</v>
       </c>
       <c r="J79" t="str">
         <v>지정제안</v>
       </c>
       <c r="K79" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L79" t="str">
-        <v>[지정제안] 링크장 바닥 유도 안내 표시 설치</v>
+        <v>(지정제안) 말하는 소화전, 소화기 도입</v>
       </c>
       <c r="M79" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N79" t="str">
-        <v>시민회관체육운영처</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O79" t="str">
-        <v>빙상부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P79" t="str">
-        <v>시민회관체육운영처 빙상부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q79" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R79" t="str">
-        <v>2025-04-014 빙상장 입구 유도선 부착</v>
+        <v/>
       </c>
       <c r="S79" t="str">
-        <v>중복 가능성 높음(채택)</v>
-      </c>
-      <c r="T79" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-04-014 빙상장 입구 유도선 부착_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I13]</v>
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
       </c>
       <c r="U79" t="str">
-        <v>기존 표시의 비교안 2025-04-014는 채택으로 확인됨. 대여실·링크장 출입구에 색상 바닥 유도선을 설치해 동선을 안내하는 목적·수단이 겹침. 실제 제안서의 안내구간·색상·시공 범위가 같은지 최종 확인 필요.</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -5560,49 +5556,49 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C80" t="str">
-        <v>2026-08-27 11:36:00</v>
+        <v>2026-08-27 15:50:00</v>
       </c>
       <c r="D80" t="str">
-        <v>오준영</v>
+        <v>김대호</v>
       </c>
       <c r="E80" t="str">
-        <v>기술7급</v>
+        <v>체육5급</v>
       </c>
       <c r="F80" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G80" t="str">
-        <v>미래전략실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H80" t="str">
-        <v>스마트정보부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I80" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="J80" t="str">
         <v>지정제안</v>
       </c>
       <c r="K80" t="str">
-        <v>제도개선</v>
+        <v>업무개선</v>
       </c>
       <c r="L80" t="str">
-        <v>[지정제안] 오픈소스 기반 전자서명 솔루션 구축</v>
+        <v>[지정제안] 전자계약 서비스 도입(단시간 강사 근로계약 체결 업무)</v>
       </c>
       <c r="M80" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N80" t="str">
-        <v>미래전략실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O80" t="str">
-        <v>스마트정보부</v>
+        <v>여가체육부</v>
       </c>
       <c r="P80" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="Q80" t="str">
         <v/>
@@ -5625,49 +5621,49 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C81" t="str">
-        <v>2026-08-27 13:16:00</v>
+        <v>2026-08-28 09:46:00</v>
       </c>
       <c r="D81" t="str">
-        <v>장소희</v>
+        <v>김민정</v>
       </c>
       <c r="E81" t="str">
-        <v>체육4급</v>
+        <v>체육6급</v>
       </c>
       <c r="F81" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G81" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H81" t="str">
-        <v>공원운영부</v>
+        <v>수영부</v>
       </c>
       <c r="I81" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J81" t="str">
         <v>지정제안</v>
       </c>
       <c r="K81" t="str">
-        <v>예산절감(수익창출)</v>
+        <v>안전</v>
       </c>
       <c r="L81" t="str">
-        <v>[지정제안] 안내데스크 탄력적 무인운영을 통한 인건비 절감 및 수익구조 개선</v>
+        <v>[지정제안] 수영장 자유수영 속도별 맞춤 레인 운영</v>
       </c>
       <c r="M81" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N81" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O81" t="str">
-        <v>공원운영부</v>
+        <v>수영부</v>
       </c>
       <c r="P81" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q81" t="str">
         <v/>
@@ -5690,49 +5686,49 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C82" t="str">
-        <v>2026-08-27 14:34:00</v>
+        <v>2026-08-28 10:14:00</v>
       </c>
       <c r="D82" t="str">
-        <v>박병진</v>
+        <v>김민정</v>
       </c>
       <c r="E82" t="str">
-        <v>행정7급(기간제)</v>
+        <v>체육6급</v>
       </c>
       <c r="F82" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G82" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H82" t="str">
-        <v>공원운영부</v>
+        <v>수영부</v>
       </c>
       <c r="I82" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J82" t="str">
         <v>지정제안</v>
       </c>
       <c r="K82" t="str">
-        <v>업무개선</v>
+        <v>지역상생</v>
       </c>
       <c r="L82" t="str">
-        <v>[지정제안] 전산·전력 마비 상황 대비 안내데스크 비상 운영 키트 배치</v>
+        <v>[지정제안] 지역사회 협력을 통한 청소년 수영강사·수상안전요원 진로체험 프로그램 운영</v>
       </c>
       <c r="M82" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N82" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O82" t="str">
-        <v>공원운영부</v>
+        <v>수영부</v>
       </c>
       <c r="P82" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q82" t="str">
         <v/>
@@ -5755,49 +5751,49 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C83" t="str">
-        <v>2026-08-27 15:26:00</v>
+        <v>2026-08-28 10:14:00</v>
       </c>
       <c r="D83" t="str">
-        <v>안경선</v>
+        <v>신정련</v>
       </c>
       <c r="E83" t="str">
-        <v>행정 4급</v>
+        <v>체육5급</v>
       </c>
       <c r="F83" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G83" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H83" t="str">
-        <v>수련관운영부</v>
+        <v>수영부</v>
       </c>
       <c r="I83" t="str">
-        <v>공원수련관관리처 수련관운영부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J83" t="str">
         <v>지정제안</v>
       </c>
       <c r="K83" t="str">
-        <v>안전</v>
+        <v>고객서비스</v>
       </c>
       <c r="L83" t="str">
-        <v>(지정제안) 말하는 소화전, 소화기 도입</v>
+        <v>(지정제안) 탈의실 락커 내 유휴공간 이용안내 홍보물 스티커 부착</v>
       </c>
       <c r="M83" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N83" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O83" t="str">
-        <v>시설지원부</v>
+        <v>수영부</v>
       </c>
       <c r="P83" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q83" t="str">
         <v/>
@@ -5820,16 +5816,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C84" t="str">
-        <v>2026-08-27 15:50:00</v>
+        <v>2026-08-28 14:49:00</v>
       </c>
       <c r="D84" t="str">
-        <v>김대호</v>
+        <v>김민정</v>
       </c>
       <c r="E84" t="str">
-        <v>체육5급</v>
+        <v>체육6급</v>
       </c>
       <c r="F84" t="str">
         <v>운영관리본부</v>
@@ -5838,19 +5834,19 @@
         <v>시민회관체육운영처</v>
       </c>
       <c r="H84" t="str">
-        <v>여가체육부</v>
+        <v>수영부</v>
       </c>
       <c r="I84" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J84" t="str">
         <v>지정제안</v>
       </c>
       <c r="K84" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L84" t="str">
-        <v>[지정제안] 전자계약 서비스 도입(단시간 강사 근로계약 체결 업무)</v>
+        <v>[지정제안] 맨발 이용객 안전을 위한 수영장 샤워실·탈의실 「유리용기ZERO」 운영</v>
       </c>
       <c r="M84" t="str">
         <v>운영관리본부</v>
@@ -5859,10 +5855,10 @@
         <v>시민회관체육운영처</v>
       </c>
       <c r="O84" t="str">
-        <v>여가체육부</v>
+        <v>수영부</v>
       </c>
       <c r="P84" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q84" t="str">
         <v/>
@@ -5885,28 +5881,28 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C85" t="str">
-        <v>2026-08-28 09:46:00</v>
+        <v>2026-08-28 16:06:00</v>
       </c>
       <c r="D85" t="str">
-        <v>김민정</v>
+        <v>신지인</v>
       </c>
       <c r="E85" t="str">
-        <v>체육6급</v>
+        <v>행정6급</v>
       </c>
       <c r="F85" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G85" t="str">
-        <v>시민회관체육운영처</v>
+        <v>미래전략실</v>
       </c>
       <c r="H85" t="str">
-        <v>수영부</v>
+        <v>미래혁신부</v>
       </c>
       <c r="I85" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>미래전략실 미래혁신부</v>
       </c>
       <c r="J85" t="str">
         <v>지정제안</v>
@@ -5915,19 +5911,19 @@
         <v>안전</v>
       </c>
       <c r="L85" t="str">
-        <v>[지정제안] 수영장 자유수영 속도별 맞춤 레인 운영</v>
+        <v>[지정제안] 경영평가 취약지표 극복을 위한 안전사고 전사 공유 체계 구축</v>
       </c>
       <c r="M85" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N85" t="str">
-        <v>시민회관체육운영처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O85" t="str">
-        <v>수영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P85" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q85" t="str">
         <v/>
@@ -5950,49 +5946,49 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C86" t="str">
-        <v>2026-08-28 10:14:00</v>
+        <v>2026-08-28 17:17:00</v>
       </c>
       <c r="D86" t="str">
-        <v>김민정</v>
+        <v>신은미</v>
       </c>
       <c r="E86" t="str">
-        <v>체육6급</v>
+        <v>행정6급</v>
       </c>
       <c r="F86" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G86" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H86" t="str">
-        <v>수영부</v>
+        <v>회계부</v>
       </c>
       <c r="I86" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 회계부</v>
       </c>
       <c r="J86" t="str">
         <v>지정제안</v>
       </c>
       <c r="K86" t="str">
-        <v>지역상생</v>
+        <v>제도개선</v>
       </c>
       <c r="L86" t="str">
-        <v>[지정제안] 지역사회 협력을 통한 청소년 수영강사·수상안전요원 진로체험 프로그램 운영</v>
+        <v>[지정제안]업무추진비 집행기준 정립을 통한 투명한 관리체계 구축</v>
       </c>
       <c r="M86" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N86" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O86" t="str">
-        <v>수영부</v>
+        <v>회계부</v>
       </c>
       <c r="P86" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 회계부</v>
       </c>
       <c r="Q86" t="str">
         <v/>
@@ -6015,49 +6011,49 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C87" t="str">
-        <v>2026-08-28 10:14:00</v>
+        <v>2026-08-28 19:01:00</v>
       </c>
       <c r="D87" t="str">
-        <v>신정련</v>
+        <v>오예림</v>
       </c>
       <c r="E87" t="str">
-        <v>체육5급</v>
+        <v>행정6급</v>
       </c>
       <c r="F87" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G87" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H87" t="str">
-        <v>수영부</v>
+        <v>인사부</v>
       </c>
       <c r="I87" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="J87" t="str">
         <v>지정제안</v>
       </c>
       <c r="K87" t="str">
-        <v>고객서비스</v>
+        <v>AI혁신</v>
       </c>
       <c r="L87" t="str">
-        <v>(지정제안) 탈의실 락커 내 유휴공간 이용안내 홍보물 스티커 부착</v>
+        <v>[지정제안] 일시고용 근로시간 통합관리용 파일 구축</v>
       </c>
       <c r="M87" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N87" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O87" t="str">
-        <v>수영부</v>
+        <v>인사부</v>
       </c>
       <c r="P87" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 인사부</v>
       </c>
       <c r="Q87" t="str">
         <v/>
@@ -6080,49 +6076,49 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C88" t="str">
-        <v>2026-08-28 14:49:00</v>
+        <v>2026-08-31 09:50:00</v>
       </c>
       <c r="D88" t="str">
-        <v>김민정</v>
+        <v>박태준</v>
       </c>
       <c r="E88" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F88" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G88" t="str">
-        <v>시민회관체육운영처</v>
+        <v>사업개발처</v>
       </c>
       <c r="H88" t="str">
-        <v>수영부</v>
+        <v>개발1부</v>
       </c>
       <c r="I88" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>사업개발처 개발1부</v>
       </c>
       <c r="J88" t="str">
         <v>지정제안</v>
       </c>
       <c r="K88" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L88" t="str">
-        <v>[지정제안] 맨발 이용객 안전을 위한 수영장 샤워실·탈의실 「유리용기ZERO」 운영</v>
+        <v>[지정제안] QR 기반 현장안전점검 시스템 구축</v>
       </c>
       <c r="M88" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N88" t="str">
-        <v>시민회관체육운영처</v>
+        <v>사업개발처</v>
       </c>
       <c r="O88" t="str">
-        <v>수영부</v>
+        <v>개발1부</v>
       </c>
       <c r="P88" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>사업개발처 개발 1부</v>
       </c>
       <c r="Q88" t="str">
         <v/>
@@ -6145,49 +6141,49 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C89" t="str">
-        <v>2026-08-28 16:06:00</v>
+        <v>2026-08-31 09:51:00</v>
       </c>
       <c r="D89" t="str">
-        <v>신지인</v>
+        <v>박태준</v>
       </c>
       <c r="E89" t="str">
-        <v>행정6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F89" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G89" t="str">
-        <v>미래전략실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H89" t="str">
-        <v>미래혁신부</v>
+        <v>개발1부</v>
       </c>
       <c r="I89" t="str">
-        <v>미래전략실 미래혁신부</v>
+        <v>사업개발처 개발1부</v>
       </c>
       <c r="J89" t="str">
         <v>지정제안</v>
       </c>
       <c r="K89" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L89" t="str">
-        <v>[지정제안] 경영평가 취약지표 극복을 위한 안전사고 전사 공유 체계 구축</v>
+        <v>[지정제안] 공사·용역 업무 단계별 표준 체크리스트 제도화</v>
       </c>
       <c r="M89" t="str">
-        <v>사장 직속</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N89" t="str">
-        <v>안전총괄단</v>
+        <v>사업개발처</v>
       </c>
       <c r="O89" t="str">
-        <v>안전총괄단</v>
+        <v>개발1부</v>
       </c>
       <c r="P89" t="str">
-        <v>안전총괄단</v>
+        <v>사업개발처 개발 1부</v>
       </c>
       <c r="Q89" t="str">
         <v/>
@@ -6210,49 +6206,49 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C90" t="str">
-        <v>2026-08-28 17:17:00</v>
+        <v>2026-08-31 09:56:00</v>
       </c>
       <c r="D90" t="str">
-        <v>신은미</v>
+        <v>장연주</v>
       </c>
       <c r="E90" t="str">
-        <v>행정6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F90" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G90" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H90" t="str">
-        <v>회계부</v>
+        <v>개발1부</v>
       </c>
       <c r="I90" t="str">
-        <v>경영지원실 회계부</v>
+        <v>사업개발처 개발1부</v>
       </c>
       <c r="J90" t="str">
         <v>지정제안</v>
       </c>
       <c r="K90" t="str">
-        <v>제도개선</v>
+        <v>고객서비스</v>
       </c>
       <c r="L90" t="str">
-        <v>[지정제안]업무추진비 집행기준 정립을 통한 투명한 관리체계 구축</v>
+        <v>[지정제안] 명함 QR코드를 활용한 부서별 업무정보 바로가기 구축</v>
       </c>
       <c r="M90" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N90" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="O90" t="str">
-        <v>회계부</v>
+        <v>개발1부</v>
       </c>
       <c r="P90" t="str">
-        <v>경영지원실 회계부</v>
+        <v>사업개발처 개발 1부</v>
       </c>
       <c r="Q90" t="str">
         <v/>
@@ -6275,28 +6271,28 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C91" t="str">
-        <v>2026-08-28 19:01:00</v>
+        <v>2026-08-31 09:59:00</v>
       </c>
       <c r="D91" t="str">
-        <v>오예림</v>
+        <v>심은혜</v>
       </c>
       <c r="E91" t="str">
-        <v>행정6급</v>
+        <v>기술 6급</v>
       </c>
       <c r="F91" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G91" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H91" t="str">
-        <v>인사부</v>
+        <v>개발2부</v>
       </c>
       <c r="I91" t="str">
-        <v>경영지원실 인사부</v>
+        <v>사업개발처 개발2부</v>
       </c>
       <c r="J91" t="str">
         <v>지정제안</v>
@@ -6305,19 +6301,19 @@
         <v>AI혁신</v>
       </c>
       <c r="L91" t="str">
-        <v>[지정제안] 일시고용 근로시간 통합관리용 파일 구축</v>
+        <v>[지정제안] AI 기반 사업정보 통합관리 시스템 구축</v>
       </c>
       <c r="M91" t="str">
         <v>경영부문</v>
       </c>
       <c r="N91" t="str">
-        <v>경영지원실</v>
+        <v>미래전략실</v>
       </c>
       <c r="O91" t="str">
-        <v>인사부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="P91" t="str">
-        <v>경영지원실 인사부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="Q91" t="str">
         <v/>
@@ -6335,70 +6331,69 @@
         <v/>
       </c>
     </row>
-    <row r="92" xml:space="preserve">
+    <row r="92">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C92" t="str">
-        <v>2026-08-31 08:14:00</v>
+        <v>2026-08-31 10:34:00</v>
       </c>
       <c r="D92" t="str">
-        <v>김성진</v>
+        <v>조성인</v>
       </c>
       <c r="E92" t="str">
-        <v>체육6급</v>
+        <v>체육 6급</v>
       </c>
       <c r="F92" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G92" t="str">
-        <v>공원수련관관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H92" t="str">
-        <v>수련관운영부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I92" t="str">
-        <v>수련관운영부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="J92" t="str">
         <v>지정제안</v>
       </c>
       <c r="K92" t="str">
-        <v>안전</v>
+        <v>제도개선</v>
       </c>
       <c r="L92" t="str">
-        <v>[지정제안] 청소년수련관 주차장 트렌치 덮개 설치를 통한 안전사고 예방</v>
+        <v>[지정제안] 시민회관 부설주차장 주차질서 확립을 위한 관리체계 개선</v>
       </c>
       <c r="M92" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N92" t="str">
-        <v>공원수련관관리처</v>
+        <v>시설관리처</v>
       </c>
       <c r="O92" t="str">
-        <v>시설지원부</v>
+        <v>주차관리부</v>
       </c>
       <c r="P92" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>시설관리처 주차관리부</v>
       </c>
       <c r="Q92" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R92" t="str">
-        <v>2025-10-134 청소년 수련관 주차장 트렌치 개선</v>
+        <v/>
       </c>
       <c r="S92" t="str">
-        <v>중복 가능성 높음(채택)</v>
-      </c>
-      <c r="T92" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-10-134 청소년 수련관 주차장 트렌치 개선_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I123]</v>
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
       </c>
       <c r="U92" t="str">
-        <v>2025-10-134는 총괄 시트와 일반제안(채택) 시트에서 채택으로 확인됨. 같은 청소년수련관 주차장의 노출 트렌치에 안전형 덮개를 설치하여 발 빠짐을 예방하는 내용으로 핵심 대상·조치가 일치함. 소재·격자와 설치구간 차이는 확인 필요.</v>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -6406,28 +6401,28 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C93" t="str">
-        <v>2026-08-31 09:50:00</v>
+        <v>2026-08-31 10:55:00</v>
       </c>
       <c r="D93" t="str">
-        <v>박태준</v>
+        <v>박자우</v>
       </c>
       <c r="E93" t="str">
-        <v>기술6급</v>
+        <v>행정6급</v>
       </c>
       <c r="F93" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="G93" t="str">
-        <v>사업개발처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H93" t="str">
-        <v>개발1부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I93" t="str">
-        <v>사업개발처 개발1부</v>
+        <v>사업계획처 판매보상부</v>
       </c>
       <c r="J93" t="str">
         <v>지정제안</v>
@@ -6436,19 +6431,19 @@
         <v>업무개선</v>
       </c>
       <c r="L93" t="str">
-        <v>[지정제안] QR 기반 현장안전점검 시스템 구축</v>
+        <v>[지정제안] 개별 게시판 검색의 비효율을 해소! 사내 시스템 통합검색 기능 구축</v>
       </c>
       <c r="M93" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N93" t="str">
-        <v>사업개발처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O93" t="str">
-        <v>개발1부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="P93" t="str">
-        <v>사업개발처 개발 1부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="Q93" t="str">
         <v/>
@@ -6471,49 +6466,49 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C94" t="str">
-        <v>2026-08-31 09:51:00</v>
+        <v>2026-08-31 11:08:00</v>
       </c>
       <c r="D94" t="str">
-        <v>박태준</v>
+        <v>이호서</v>
       </c>
       <c r="E94" t="str">
-        <v>기술6급</v>
+        <v>행정6급</v>
       </c>
       <c r="F94" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="G94" t="str">
-        <v>사업개발처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H94" t="str">
-        <v>개발1부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="I94" t="str">
-        <v>사업개발처 개발1부</v>
+        <v>사업계획처 판매보상부</v>
       </c>
       <c r="J94" t="str">
         <v>지정제안</v>
       </c>
       <c r="K94" t="str">
-        <v>업무개선</v>
+        <v>지역상생</v>
       </c>
       <c r="L94" t="str">
-        <v>[지정제안] 공사·용역 업무 단계별 표준 체크리스트 제도화</v>
+        <v>[지정제안] 「시민주거복지상담소」 운영을 통한 주거복지 실현</v>
       </c>
       <c r="M94" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="N94" t="str">
-        <v>사업개발처</v>
+        <v>사업계획처</v>
       </c>
       <c r="O94" t="str">
-        <v>개발1부</v>
+        <v>판매·보상부</v>
       </c>
       <c r="P94" t="str">
-        <v>사업개발처 개발 1부</v>
+        <v>사업계획처 판매·보상부</v>
       </c>
       <c r="Q94" t="str">
         <v/>
@@ -6536,49 +6531,49 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C95" t="str">
-        <v>2026-08-31 09:56:00</v>
+        <v>2026-08-31 11:14:00</v>
       </c>
       <c r="D95" t="str">
-        <v>장연주</v>
+        <v>김은지</v>
       </c>
       <c r="E95" t="str">
-        <v>기술6급</v>
+        <v>행정6급</v>
       </c>
       <c r="F95" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G95" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H95" t="str">
-        <v>개발1부</v>
+        <v>회계부</v>
       </c>
       <c r="I95" t="str">
-        <v>사업개발처 개발1부</v>
+        <v>경영지원실 회계부</v>
       </c>
       <c r="J95" t="str">
         <v>지정제안</v>
       </c>
       <c r="K95" t="str">
-        <v>고객서비스</v>
+        <v>지역상생</v>
       </c>
       <c r="L95" t="str">
-        <v>[지정제안] 명함 QR코드를 활용한 부서별 업무정보 바로가기 구축</v>
+        <v>[지정제안] 경기도장애인생산품판매시설과 업무협약(MOU)을 통한 장애인생산품 우선구매 활성화</v>
       </c>
       <c r="M95" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N95" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O95" t="str">
-        <v>개발1부</v>
+        <v>회계부</v>
       </c>
       <c r="P95" t="str">
-        <v>사업개발처 개발 1부</v>
+        <v>경영지원실 회계부</v>
       </c>
       <c r="Q95" t="str">
         <v/>
@@ -6601,28 +6596,28 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C96" t="str">
-        <v>2026-08-31 09:59:00</v>
+        <v>2026-08-31 11:18:00</v>
       </c>
       <c r="D96" t="str">
-        <v>심은혜</v>
+        <v>김진겸</v>
       </c>
       <c r="E96" t="str">
-        <v>기술 6급</v>
+        <v>행정5급</v>
       </c>
       <c r="F96" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G96" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H96" t="str">
-        <v>개발2부</v>
+        <v>재무부</v>
       </c>
       <c r="I96" t="str">
-        <v>사업개발처 개발2부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="J96" t="str">
         <v>지정제안</v>
@@ -6631,19 +6626,19 @@
         <v>AI혁신</v>
       </c>
       <c r="L96" t="str">
-        <v>[지정제안] AI 기반 사업정보 통합관리 시스템 구축</v>
+        <v>[지정제안] AI가 그리는 재무기상도 "불확실성을 넘어서는 선제적 리스크 조기경보 체계" 구축</v>
       </c>
       <c r="M96" t="str">
         <v>경영부문</v>
       </c>
       <c r="N96" t="str">
-        <v>미래전략실</v>
+        <v>경영지원실</v>
       </c>
       <c r="O96" t="str">
-        <v>스마트정보부</v>
+        <v>재무부</v>
       </c>
       <c r="P96" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="Q96" t="str">
         <v/>
@@ -6661,21 +6656,21 @@
         <v/>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C97" t="str">
-        <v>2026-08-31 10:34:00</v>
+        <v>2026-08-31 13:33:00</v>
       </c>
       <c r="D97" t="str">
-        <v>조성인</v>
+        <v>김경민</v>
       </c>
       <c r="E97" t="str">
-        <v>체육 6급</v>
+        <v>체육6급</v>
       </c>
       <c r="F97" t="str">
         <v>운영관리본부</v>
@@ -6684,31 +6679,31 @@
         <v>시민회관체육운영처</v>
       </c>
       <c r="H97" t="str">
-        <v>여가체육부</v>
+        <v>수영부</v>
       </c>
       <c r="I97" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="J97" t="str">
         <v>지정제안</v>
       </c>
       <c r="K97" t="str">
-        <v>제도개선</v>
+        <v>업무개선</v>
       </c>
       <c r="L97" t="str">
-        <v>[지정제안] 시민회관 부설주차장 주차질서 확립을 위한 관리체계 개선</v>
+        <v>[지정제] AI 기반 수영장 일일점검 및 전자결재 시스템 구축</v>
       </c>
       <c r="M97" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="N97" t="str">
-        <v>시설관리처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O97" t="str">
-        <v>주차관리부</v>
+        <v>수영부</v>
       </c>
       <c r="P97" t="str">
-        <v>시설관리처 주차관리부</v>
+        <v>시민회관체육운영처 수영부</v>
       </c>
       <c r="Q97" t="str">
         <v/>
@@ -6717,13 +6712,14 @@
         <v/>
       </c>
       <c r="S97" t="str">
-        <v/>
-      </c>
-      <c r="T97" t="str">
-        <v/>
+        <v>유사(채택)</v>
+      </c>
+      <c r="T97" t="str" xml:space="preserve">
+        <v xml:space="preserve">2025-10-190 체육시설 디지털 안전관리 시스템 도입_x000d_
+심사결과: 채택 [2025년 제안 총괄 !I173]</v>
       </c>
       <c r="U97" t="str">
-        <v/>
+        <v>2025-10-190은 채택으로 확인됨. 모바일 안전점검·위험요인 사진 신고·이력관리 기능이 이번 수영장 점검·조치이력과 겹치지만, 부서장 전자결재와 수영장 특화 범위는 추가됨. 단순 중복 확정이 아닌 기능범위 차이를 확인할 대상임. 2022-12-167은 채택결과 미확인으로 근거에서 제외함.</v>
       </c>
     </row>
     <row r="98">
@@ -6731,49 +6727,49 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C98" t="str">
-        <v>2026-08-31 10:55:00</v>
+        <v>2026-08-31 13:47:00</v>
       </c>
       <c r="D98" t="str">
-        <v>박자우</v>
+        <v>신송식</v>
       </c>
       <c r="E98" t="str">
-        <v>행정6급</v>
+        <v>기술4급</v>
       </c>
       <c r="F98" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="G98" t="str">
-        <v>사업계획처</v>
+        <v>사업개발처</v>
       </c>
       <c r="H98" t="str">
-        <v>판매·보상부</v>
+        <v>기술지원부</v>
       </c>
       <c r="I98" t="str">
-        <v>사업계획처 판매보상부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="J98" t="str">
         <v>지정제안</v>
       </c>
       <c r="K98" t="str">
-        <v>업무개선</v>
+        <v>기타</v>
       </c>
       <c r="L98" t="str">
-        <v>[지정제안] 개별 게시판 검색의 비효율을 해소! 사내 시스템 통합검색 기능 구축</v>
+        <v>경차 전용 주차구역 이용질서 준수유도</v>
       </c>
       <c r="M98" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N98" t="str">
-        <v>미래전략실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O98" t="str">
-        <v>스마트정보부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P98" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q98" t="str">
         <v/>
@@ -6796,49 +6792,49 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C99" t="str">
-        <v>2026-08-31 11:08:00</v>
+        <v>2026-08-31 14:17:00</v>
       </c>
       <c r="D99" t="str">
-        <v>이호서</v>
+        <v>이승호</v>
       </c>
       <c r="E99" t="str">
-        <v>행정6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F99" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="G99" t="str">
-        <v>사업계획처</v>
+        <v>사업개발처</v>
       </c>
       <c r="H99" t="str">
-        <v>판매·보상부</v>
+        <v>기술지원부</v>
       </c>
       <c r="I99" t="str">
-        <v>사업계획처 판매보상부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="J99" t="str">
         <v>지정제안</v>
       </c>
       <c r="K99" t="str">
-        <v>지역상생</v>
+        <v>시설개선</v>
       </c>
       <c r="L99" t="str">
-        <v>[지정제안] 「시민주거복지상담소」 운영을 통한 주거복지 실현</v>
+        <v>비상벨 및 CCTV 연동을 통한 스마트 안전관제 시스템 구축</v>
       </c>
       <c r="M99" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="N99" t="str">
-        <v>사업계획처</v>
+        <v>사업개발처</v>
       </c>
       <c r="O99" t="str">
-        <v>판매·보상부</v>
+        <v>기술지원부</v>
       </c>
       <c r="P99" t="str">
-        <v>사업계획처 판매·보상부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="Q99" t="str">
         <v/>
@@ -6861,13 +6857,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C100" t="str">
-        <v>2026-08-31 11:14:00</v>
+        <v>2026-08-31 14:19:00</v>
       </c>
       <c r="D100" t="str">
-        <v>김은지</v>
+        <v>이희진</v>
       </c>
       <c r="E100" t="str">
         <v>행정6급</v>
@@ -6879,10 +6875,10 @@
         <v>경영지원실</v>
       </c>
       <c r="H100" t="str">
-        <v>회계부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I100" t="str">
-        <v>경영지원실 회계부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J100" t="str">
         <v>지정제안</v>
@@ -6891,7 +6887,7 @@
         <v>지역상생</v>
       </c>
       <c r="L100" t="str">
-        <v>[지정제안] 경기도장애인생산품판매시설과 업무협약(MOU)을 통한 장애인생산품 우선구매 활성화</v>
+        <v>「지정제안」 임직원 참여형 지역상생 실천 릴레이 캠페인 추진</v>
       </c>
       <c r="M100" t="str">
         <v>경영부문</v>
@@ -6900,10 +6896,10 @@
         <v>경영지원실</v>
       </c>
       <c r="O100" t="str">
-        <v>회계부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P100" t="str">
-        <v>경영지원실 회계부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q100" t="str">
         <v/>
@@ -6926,49 +6922,49 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C101" t="str">
-        <v>2026-08-31 11:18:00</v>
+        <v>2026-08-31 14:19:00</v>
       </c>
       <c r="D101" t="str">
-        <v>김진겸</v>
+        <v>최지연</v>
       </c>
       <c r="E101" t="str">
-        <v>행정5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F101" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G101" t="str">
-        <v>경영지원실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H101" t="str">
-        <v>재무부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I101" t="str">
-        <v>경영지원실 재무부</v>
+        <v>여가체육부</v>
       </c>
       <c r="J101" t="str">
         <v>지정제안</v>
       </c>
       <c r="K101" t="str">
-        <v>AI혁신</v>
+        <v>제도개선</v>
       </c>
       <c r="L101" t="str">
-        <v>[지정제안] AI가 그리는 재무기상도 "불확실성을 넘어서는 선제적 리스크 조기경보 체계" 구축</v>
+        <v>[지정제안]에너지절약 실천 체크리스트 일일 기안 폐지 및 실효성 중심의 점검체계 개편</v>
       </c>
       <c r="M101" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N101" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O101" t="str">
-        <v>재무부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P101" t="str">
-        <v>경영지원실 재무부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q101" t="str">
         <v/>
@@ -6991,49 +6987,49 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C102" t="str">
-        <v>2026-08-31 13:33:00</v>
+        <v>2026-08-31 14:21:00</v>
       </c>
       <c r="D102" t="str">
-        <v>김경민</v>
+        <v>우세림</v>
       </c>
       <c r="E102" t="str">
         <v>체육6급</v>
       </c>
       <c r="F102" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G102" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H102" t="str">
-        <v>수영부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I102" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J102" t="str">
         <v>지정제안</v>
       </c>
       <c r="K102" t="str">
-        <v>업무개선</v>
+        <v>AI혁신</v>
       </c>
       <c r="L102" t="str">
-        <v>[지정제] AI 기반 수영장 일일점검 및 전자결재 시스템 구축</v>
+        <v>[지정제안]AI TTS를 활용한 아침방송 자동화 및 업무 효율화</v>
       </c>
       <c r="M102" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N102" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O102" t="str">
-        <v>수영부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P102" t="str">
-        <v>시민회관체육운영처 수영부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q102" t="str">
         <v/>
@@ -7045,11 +7041,11 @@
         <v>유사(채택)</v>
       </c>
       <c r="T102" t="str" xml:space="preserve">
-        <v xml:space="preserve">2025-10-190 체육시설 디지털 안전관리 시스템 도입_x000d_
-심사결과: 채택 [2025년 제안 총괄 !I173]</v>
+        <v xml:space="preserve">관문공원 자동안내방송 프로그램(TTS) 설치_x000d_
+심사결과: 채택 [2021년 제안!I66, 연번 63]</v>
       </c>
       <c r="U102" t="str">
-        <v>2025-10-190은 채택으로 확인됨. 모바일 안전점검·위험요인 사진 신고·이력관리 기능이 이번 수영장 점검·조치이력과 겹치지만, 부서장 전자결재와 수영장 특화 범위는 추가됨. 단순 중복 확정이 아닌 기능범위 차이를 확인할 대상임. 2022-12-167은 채택결과 미확인으로 근거에서 제외함.</v>
+        <v>관문공원 자동안내방송 TTS 제안은 2021년 제안 시트 66행에서 채택으로 확인됨. 문자를 음성으로 변환하여 육성 방송을 대체·표준화하는 방식은 같으나 이번은 사내 아침방송에 AI 음성·원고검토·편집·예약송출을 적용함. 적용업무와 추가 절차의 차별성 검토 필요.</v>
       </c>
     </row>
     <row r="103">
@@ -7057,49 +7053,49 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C103" t="str">
-        <v>2026-08-31 13:47:00</v>
+        <v>2026-08-31 14:22:00</v>
       </c>
       <c r="D103" t="str">
-        <v>신송식</v>
+        <v>우세림</v>
       </c>
       <c r="E103" t="str">
-        <v>기술4급</v>
+        <v>체육6급</v>
       </c>
       <c r="F103" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G103" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H103" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I103" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J103" t="str">
         <v>지정제안</v>
       </c>
       <c r="K103" t="str">
-        <v>기타</v>
+        <v>지역상생</v>
       </c>
       <c r="L103" t="str">
-        <v>경차 전용 주차구역 이용질서 준수유도</v>
+        <v>[지정제안] 정원가산업무비 지역화폐 지급을 통한 지역경제 활성화</v>
       </c>
       <c r="M103" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N103" t="str">
-        <v>시설관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O103" t="str">
-        <v>시설운영부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P103" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q103" t="str">
         <v/>
@@ -7122,49 +7118,49 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C104" t="str">
-        <v>2026-08-31 14:17:00</v>
+        <v>2026-08-31 14:24:00</v>
       </c>
       <c r="D104" t="str">
-        <v>이승호</v>
+        <v>우세림</v>
       </c>
       <c r="E104" t="str">
-        <v>기술6급</v>
+        <v>체육6급</v>
       </c>
       <c r="F104" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G104" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H104" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I104" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J104" t="str">
         <v>지정제안</v>
       </c>
       <c r="K104" t="str">
-        <v>시설개선</v>
+        <v>지역상생</v>
       </c>
       <c r="L104" t="str">
-        <v>비상벨 및 CCTV 연동을 통한 스마트 안전관제 시스템 구축</v>
+        <v>[지정제안]국내 벤치마킹 연계 지역경제 활성화 추진</v>
       </c>
       <c r="M104" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N104" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O104" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P104" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q104" t="str">
         <v/>
@@ -7187,49 +7183,49 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C105" t="str">
-        <v>2026-08-31 14:19:00</v>
+        <v>2026-08-31 14:24:00</v>
       </c>
       <c r="D105" t="str">
-        <v>이희진</v>
+        <v>이승호</v>
       </c>
       <c r="E105" t="str">
-        <v>행정6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F105" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G105" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H105" t="str">
-        <v>총무행정부</v>
+        <v>기술지원부</v>
       </c>
       <c r="I105" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="J105" t="str">
         <v>지정제안</v>
       </c>
       <c r="K105" t="str">
-        <v>지역상생</v>
+        <v>업무개선</v>
       </c>
       <c r="L105" t="str">
-        <v>「지정제안」 임직원 참여형 지역상생 실천 릴레이 캠페인 추진</v>
+        <v>담당자 경험 중심의 건설사업 리스크 관리를 AI·데이터 기반 관리체계로 전환</v>
       </c>
       <c r="M105" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N105" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="O105" t="str">
-        <v>총무행정부</v>
+        <v>기술지원부</v>
       </c>
       <c r="P105" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="Q105" t="str">
         <v/>
@@ -7252,49 +7248,49 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C106" t="str">
-        <v>2026-08-31 14:19:00</v>
+        <v>2026-08-31 14:31:00</v>
       </c>
       <c r="D106" t="str">
-        <v>최지연</v>
+        <v>이희진</v>
       </c>
       <c r="E106" t="str">
-        <v>체육5급</v>
+        <v>행정6급</v>
       </c>
       <c r="F106" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G106" t="str">
-        <v>시민회관체육운영처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H106" t="str">
-        <v>여가체육부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I106" t="str">
-        <v>여가체육부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J106" t="str">
         <v>지정제안</v>
       </c>
       <c r="K106" t="str">
-        <v>제도개선</v>
+        <v>지역상생</v>
       </c>
       <c r="L106" t="str">
-        <v>[지정제안]에너지절약 실천 체크리스트 일일 기안 폐지 및 실효성 중심의 점검체계 개편</v>
+        <v>「지정제안」 재난 구호 지원단 인력풀 운영</v>
       </c>
       <c r="M106" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N106" t="str">
-        <v>시설관리처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O106" t="str">
-        <v>시설운영부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P106" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q106" t="str">
         <v/>
@@ -7312,54 +7308,54 @@
         <v/>
       </c>
     </row>
-    <row r="107" xml:space="preserve">
+    <row r="107">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C107" t="str">
-        <v>2026-08-31 14:21:00</v>
+        <v>2026-08-31 14:32:00</v>
       </c>
       <c r="D107" t="str">
-        <v>우세림</v>
+        <v>박명진</v>
       </c>
       <c r="E107" t="str">
-        <v>체육6급</v>
+        <v>행정5급</v>
       </c>
       <c r="F107" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G107" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H107" t="str">
-        <v>총무행정부</v>
+        <v>공원운영부</v>
       </c>
       <c r="I107" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="J107" t="str">
         <v>지정제안</v>
       </c>
       <c r="K107" t="str">
-        <v>AI혁신</v>
+        <v>고객서비스</v>
       </c>
       <c r="L107" t="str">
-        <v>[지정제안]AI TTS를 활용한 아침방송 자동화 및 업무 효율화</v>
+        <v>관문체육공원 연계 「과천 숲 회복 스테이션」</v>
       </c>
       <c r="M107" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N107" t="str">
-        <v>경영지원실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O107" t="str">
-        <v>총무행정부</v>
+        <v>공원운영부</v>
       </c>
       <c r="P107" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>공원수련관관리처 공원운영부</v>
       </c>
       <c r="Q107" t="str">
         <v/>
@@ -7368,64 +7364,63 @@
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T107" t="str" xml:space="preserve">
-        <v xml:space="preserve">관문공원 자동안내방송 프로그램(TTS) 설치_x000d_
-심사결과: 채택 [2021년 제안!I66, 연번 63]</v>
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
       </c>
       <c r="U107" t="str">
-        <v>관문공원 자동안내방송 TTS 제안은 2021년 제안 시트 66행에서 채택으로 확인됨. 문자를 음성으로 변환하여 육성 방송을 대체·표준화하는 방식은 같으나 이번은 사내 아침방송에 AI 음성·원고검토·편집·예약송출을 적용함. 적용업무와 추가 절차의 차별성 검토 필요.</v>
-      </c>
-    </row>
-    <row r="108">
+        <v/>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C108" t="str">
-        <v>2026-08-31 14:22:00</v>
+        <v>2026-08-31 14:42:00</v>
       </c>
       <c r="D108" t="str">
-        <v>우세림</v>
+        <v>김선호</v>
       </c>
       <c r="E108" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F108" t="str">
         <v>경영부문</v>
       </c>
       <c r="G108" t="str">
-        <v>경영지원실</v>
+        <v>미래전략실</v>
       </c>
       <c r="H108" t="str">
-        <v>총무행정부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="I108" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="J108" t="str">
         <v>지정제안</v>
       </c>
       <c r="K108" t="str">
-        <v>지역상생</v>
+        <v>AI혁신</v>
       </c>
       <c r="L108" t="str">
-        <v>[지정제안] 정원가산업무비 지역화폐 지급을 통한 지역경제 활성화</v>
+        <v>[지정제안]카카오톡 챗봇 연계형 보이는 ARS 서비스 구축</v>
       </c>
       <c r="M108" t="str">
         <v>경영부문</v>
       </c>
       <c r="N108" t="str">
-        <v>경영지원실</v>
+        <v>미래전략실</v>
       </c>
       <c r="O108" t="str">
-        <v>총무행정부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="P108" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="Q108" t="str">
         <v/>
@@ -7434,13 +7429,14 @@
         <v/>
       </c>
       <c r="S108" t="str">
-        <v/>
-      </c>
-      <c r="T108" t="str">
-        <v/>
+        <v>유사(채택)</v>
+      </c>
+      <c r="T108" t="str" xml:space="preserve">
+        <v xml:space="preserve">2024-12-291 보이는 ARS 연결 시스템_x000d_
+심사결과: 채택 [2024년 제안!I154]</v>
       </c>
       <c r="U108" t="str">
-        <v/>
+        <v>보이는 ARS 연결 시스템(2024-12-291)은 채택으로 확인됨. 화면 메뉴·시설 안내·상담원 연결 기능이 겹치며 이번은 챗봇 링크 알림톡과 음성 트랙 유지를 결합함. ARS 기능 중복과 새 연계 흐름의 차별성을 나누어 검토해야 함. 2024-07-096은 불채택, 2025-06-065는 과락3명으로 채택 근거에서 제외함.</v>
       </c>
     </row>
     <row r="109">
@@ -7448,49 +7444,49 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C109" t="str">
-        <v>2026-08-31 14:24:00</v>
+        <v>2026-08-31 14:43:00</v>
       </c>
       <c r="D109" t="str">
-        <v>우세림</v>
+        <v>이우익</v>
       </c>
       <c r="E109" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F109" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G109" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="H109" t="str">
-        <v>총무행정부</v>
+        <v>시설운영부</v>
       </c>
       <c r="I109" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>시설운영부</v>
       </c>
       <c r="J109" t="str">
         <v>지정제안</v>
       </c>
       <c r="K109" t="str">
-        <v>지역상생</v>
+        <v>안전사고 예방</v>
       </c>
       <c r="L109" t="str">
-        <v>[지정제안]국내 벤치마킹 연계 지역경제 활성화 추진</v>
+        <v>[지정제안] 시민회관 전력감시제어설비 교체를 통한 안전사고 예방</v>
       </c>
       <c r="M109" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N109" t="str">
-        <v>경영지원실</v>
+        <v>시설관리처</v>
       </c>
       <c r="O109" t="str">
-        <v>총무행정부</v>
+        <v>시설운영부</v>
       </c>
       <c r="P109" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q109" t="str">
         <v/>
@@ -7513,49 +7509,49 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C110" t="str">
-        <v>2026-08-31 14:24:00</v>
+        <v>2026-08-31 14:57:00</v>
       </c>
       <c r="D110" t="str">
-        <v>이승호</v>
+        <v>김동환</v>
       </c>
       <c r="E110" t="str">
         <v>기술6급</v>
       </c>
       <c r="F110" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G110" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="H110" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="I110" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="J110" t="str">
         <v>지정제안</v>
       </c>
       <c r="K110" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L110" t="str">
-        <v>담당자 경험 중심의 건설사업 리스크 관리를 AI·데이터 기반 관리체계로 전환</v>
+        <v>[지정제안] 전기자전거 안전사고 예방을 위한 안전모 비치</v>
       </c>
       <c r="M110" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N110" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O110" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P110" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q110" t="str">
         <v/>
@@ -7578,16 +7574,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C111" t="str">
-        <v>2026-08-31 14:31:00</v>
+        <v>2026-08-31 15:08:00</v>
       </c>
       <c r="D111" t="str">
-        <v>이희진</v>
+        <v>이현</v>
       </c>
       <c r="E111" t="str">
-        <v>행정6급</v>
+        <v>체육6급</v>
       </c>
       <c r="F111" t="str">
         <v>경영부문</v>
@@ -7596,19 +7592,19 @@
         <v>경영지원실</v>
       </c>
       <c r="H111" t="str">
-        <v>총무행정부</v>
+        <v>재무부</v>
       </c>
       <c r="I111" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="J111" t="str">
         <v>지정제안</v>
       </c>
       <c r="K111" t="str">
-        <v>지역상생</v>
+        <v>AI혁신</v>
       </c>
       <c r="L111" t="str">
-        <v>「지정제안」 재난 구호 지원단 인력풀 운영</v>
+        <v>[지정제안] 계약정보공개 방법 개선</v>
       </c>
       <c r="M111" t="str">
         <v>경영부문</v>
@@ -7617,10 +7613,10 @@
         <v>경영지원실</v>
       </c>
       <c r="O111" t="str">
-        <v>총무행정부</v>
+        <v>재무부</v>
       </c>
       <c r="P111" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>경영지원실 재무부</v>
       </c>
       <c r="Q111" t="str">
         <v/>
@@ -7643,16 +7639,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C112" t="str">
-        <v>2026-08-31 14:32:00</v>
+        <v>2026-08-31 15:15:00</v>
       </c>
       <c r="D112" t="str">
-        <v>박명진</v>
+        <v>임용섭</v>
       </c>
       <c r="E112" t="str">
-        <v>행정5급</v>
+        <v>체육5급</v>
       </c>
       <c r="F112" t="str">
         <v>운영관리본부</v>
@@ -7661,19 +7657,19 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="H112" t="str">
-        <v>공원운영부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="I112" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>수련관운영부</v>
       </c>
       <c r="J112" t="str">
         <v>지정제안</v>
       </c>
       <c r="K112" t="str">
-        <v>고객서비스</v>
+        <v>안전</v>
       </c>
       <c r="L112" t="str">
-        <v>관문체육공원 연계 「과천 숲 회복 스테이션」</v>
+        <v>[지정제안] 청소년수련관 체육관 사각지대 CCTV설치</v>
       </c>
       <c r="M112" t="str">
         <v>운영관리본부</v>
@@ -7682,10 +7678,10 @@
         <v>공원수련관관리처</v>
       </c>
       <c r="O112" t="str">
-        <v>공원운영부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P112" t="str">
-        <v>공원수련관관리처 공원운영부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q112" t="str">
         <v/>
@@ -7703,54 +7699,54 @@
         <v/>
       </c>
     </row>
-    <row r="113" xml:space="preserve">
+    <row r="113">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C113" t="str">
-        <v>2026-08-31 14:42:00</v>
+        <v>2026-08-31 15:58:00</v>
       </c>
       <c r="D113" t="str">
-        <v>김선호</v>
+        <v>이승진</v>
       </c>
       <c r="E113" t="str">
         <v>기술6급</v>
       </c>
       <c r="F113" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G113" t="str">
-        <v>미래전략실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="H113" t="str">
-        <v>스마트정보부</v>
+        <v>시설지원부</v>
       </c>
       <c r="I113" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="J113" t="str">
         <v>지정제안</v>
       </c>
       <c r="K113" t="str">
-        <v>AI혁신</v>
+        <v>안전</v>
       </c>
       <c r="L113" t="str">
-        <v>[지정제안]카카오톡 챗봇 연계형 보이는 ARS 서비스 구축</v>
+        <v>[지정제안] 스마트빗물받이덮개 설치</v>
       </c>
       <c r="M113" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N113" t="str">
-        <v>미래전략실</v>
+        <v>공원수련관관리처</v>
       </c>
       <c r="O113" t="str">
-        <v>스마트정보부</v>
+        <v>시설지원부</v>
       </c>
       <c r="P113" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>공원수련관관리처 시설지원부</v>
       </c>
       <c r="Q113" t="str">
         <v/>
@@ -7759,14 +7755,13 @@
         <v/>
       </c>
       <c r="S113" t="str">
-        <v>유사(채택)</v>
-      </c>
-      <c r="T113" t="str" xml:space="preserve">
-        <v xml:space="preserve">2024-12-291 보이는 ARS 연결 시스템_x000d_
-심사결과: 채택 [2024년 제안!I154]</v>
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
       </c>
       <c r="U113" t="str">
-        <v>보이는 ARS 연결 시스템(2024-12-291)은 채택으로 확인됨. 화면 메뉴·시설 안내·상담원 연결 기능이 겹치며 이번은 챗봇 링크 알림톡과 음성 트랙 유지를 결합함. ARS 기능 중복과 새 연계 흐름의 차별성을 나누어 검토해야 함. 2024-07-096은 불채택, 2025-06-065는 과락3명으로 채택 근거에서 제외함.</v>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -7774,49 +7769,49 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C114" t="str">
-        <v>2026-08-31 14:43:00</v>
+        <v>2026-08-31 16:02:00</v>
       </c>
       <c r="D114" t="str">
-        <v>이우익</v>
+        <v>최윤호</v>
       </c>
       <c r="E114" t="str">
         <v>기술6급</v>
       </c>
       <c r="F114" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G114" t="str">
-        <v>시설관리처</v>
+        <v>사업개발처</v>
       </c>
       <c r="H114" t="str">
-        <v>시설운영부</v>
+        <v>기술지원부</v>
       </c>
       <c r="I114" t="str">
-        <v>시설운영부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="J114" t="str">
         <v>지정제안</v>
       </c>
       <c r="K114" t="str">
-        <v>안전사고 예방</v>
+        <v>AI혁신</v>
       </c>
       <c r="L114" t="str">
-        <v>[지정제안] 시민회관 전력감시제어설비 교체를 통한 안전사고 예방</v>
+        <v>[지정제안] 건설현장 디지털 기반 동영상 공정(안전) 관리 도입</v>
       </c>
       <c r="M114" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N114" t="str">
-        <v>시설관리처</v>
+        <v>사업개발처</v>
       </c>
       <c r="O114" t="str">
-        <v>시설운영부</v>
+        <v>기술지원부</v>
       </c>
       <c r="P114" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>사업개발처 기술지원부</v>
       </c>
       <c r="Q114" t="str">
         <v/>
@@ -7839,49 +7834,49 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C115" t="str">
-        <v>2026-08-31 14:57:00</v>
+        <v>2026-08-31 16:04:00</v>
       </c>
       <c r="D115" t="str">
-        <v>김동환</v>
+        <v>김효정</v>
       </c>
       <c r="E115" t="str">
         <v>기술6급</v>
       </c>
       <c r="F115" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G115" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H115" t="str">
-        <v>총무행정부</v>
+        <v>개발2부</v>
       </c>
       <c r="I115" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>사업개발처 개발2부</v>
       </c>
       <c r="J115" t="str">
         <v>지정제안</v>
       </c>
       <c r="K115" t="str">
-        <v>안전</v>
+        <v>업무개선</v>
       </c>
       <c r="L115" t="str">
-        <v>[지정제안] 전기자전거 안전사고 예방을 위한 안전모 비치</v>
+        <v>[지정제안] 설계용역 과업변경에 따른 계약금액 조정기준 마련</v>
       </c>
       <c r="M115" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N115" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="O115" t="str">
-        <v>총무행정부</v>
+        <v>개발2부</v>
       </c>
       <c r="P115" t="str">
-        <v>경영지원실 총무행정부</v>
+        <v>사업개발처 개발 2부</v>
       </c>
       <c r="Q115" t="str">
         <v/>
@@ -7904,49 +7899,49 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C116" t="str">
-        <v>2026-08-31 15:08:00</v>
+        <v>2026-08-31 16:06:00</v>
       </c>
       <c r="D116" t="str">
-        <v>이현</v>
+        <v>김효정</v>
       </c>
       <c r="E116" t="str">
-        <v>체육6급</v>
+        <v>기술6급</v>
       </c>
       <c r="F116" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G116" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H116" t="str">
-        <v>재무부</v>
+        <v>개발2부</v>
       </c>
       <c r="I116" t="str">
-        <v>경영지원실 재무부</v>
+        <v>사업개발처 개발2부</v>
       </c>
       <c r="J116" t="str">
         <v>지정제안</v>
       </c>
       <c r="K116" t="str">
-        <v>AI혁신</v>
+        <v>업무개선</v>
       </c>
       <c r="L116" t="str">
-        <v>[지정제안] 계약정보공개 방법 개선</v>
+        <v>[지정제안] 공사근로자 노무비 청구 및 지급관리 기준 마련</v>
       </c>
       <c r="M116" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N116" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="O116" t="str">
-        <v>재무부</v>
+        <v>개발2부</v>
       </c>
       <c r="P116" t="str">
-        <v>경영지원실 재무부</v>
+        <v>사업개발처 개발 2부</v>
       </c>
       <c r="Q116" t="str">
         <v/>
@@ -7969,28 +7964,28 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C117" t="str">
-        <v>2026-08-31 15:15:00</v>
+        <v>2026-08-31 16:22:00</v>
       </c>
       <c r="D117" t="str">
-        <v>임용섭</v>
+        <v>박소원</v>
       </c>
       <c r="E117" t="str">
-        <v>체육5급</v>
+        <v>기술6급</v>
       </c>
       <c r="F117" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G117" t="str">
-        <v>공원수련관관리처</v>
+        <v>미래전략실</v>
       </c>
       <c r="H117" t="str">
-        <v>수련관운영부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="I117" t="str">
-        <v>수련관운영부</v>
+        <v>미래전략실 스마트보부</v>
       </c>
       <c r="J117" t="str">
         <v>지정제안</v>
@@ -7999,19 +7994,19 @@
         <v>안전</v>
       </c>
       <c r="L117" t="str">
-        <v>[지정제안] 청소년수련관 체육관 사각지대 CCTV설치</v>
+        <v>[지정제안] AI 기반 실시간 인원관리시스템을 활용한 체육시설 안전관리 강화</v>
       </c>
       <c r="M117" t="str">
-        <v>운영관리본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N117" t="str">
-        <v>공원수련관관리처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O117" t="str">
-        <v>시설지원부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P117" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q117" t="str">
         <v/>
@@ -8034,49 +8029,49 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C118" t="str">
-        <v>2026-08-31 15:58:00</v>
+        <v>2026-08-31 16:25:00</v>
       </c>
       <c r="D118" t="str">
-        <v>이승진</v>
+        <v>박소원</v>
       </c>
       <c r="E118" t="str">
         <v>기술6급</v>
       </c>
       <c r="F118" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="G118" t="str">
-        <v>공원수련관관리처</v>
+        <v>미래전략실</v>
       </c>
       <c r="H118" t="str">
-        <v>시설지원부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="I118" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="J118" t="str">
         <v>지정제안</v>
       </c>
       <c r="K118" t="str">
-        <v>안전</v>
+        <v>AI혁신</v>
       </c>
       <c r="L118" t="str">
-        <v>[지정제안] 스마트빗물받이덮개 설치</v>
+        <v>[지정제안] 개인정보 수집·이용 동의서 점검 에이전트 구축</v>
       </c>
       <c r="M118" t="str">
-        <v>운영관리본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N118" t="str">
-        <v>공원수련관관리처</v>
+        <v>미래전략실</v>
       </c>
       <c r="O118" t="str">
-        <v>시설지원부</v>
+        <v>스마트정보부</v>
       </c>
       <c r="P118" t="str">
-        <v>공원수련관관리처 시설지원부</v>
+        <v>미래전략실 스마트정보부</v>
       </c>
       <c r="Q118" t="str">
         <v/>
@@ -8099,10 +8094,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C119" t="str">
-        <v>2026-08-31 16:02:00</v>
+        <v>2026-08-31 16:31:00</v>
       </c>
       <c r="D119" t="str">
         <v>최윤호</v>
@@ -8129,7 +8124,7 @@
         <v>AI혁신</v>
       </c>
       <c r="L119" t="str">
-        <v>[지정제안] 건설현장 디지털 기반 동영상 공정(안전) 관리 도입</v>
+        <v>[지정제안] 설계변경 실정보고 등 오류 파악을 위한 AI감리 도입</v>
       </c>
       <c r="M119" t="str">
         <v>개발사업본부</v>
@@ -8164,13 +8159,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C120" t="str">
-        <v>2026-08-31 16:04:00</v>
+        <v>2026-08-31 16:36:00</v>
       </c>
       <c r="D120" t="str">
-        <v>김효정</v>
+        <v>한효진</v>
       </c>
       <c r="E120" t="str">
         <v>기술6급</v>
@@ -8179,34 +8174,34 @@
         <v>개발사업본부</v>
       </c>
       <c r="G120" t="str">
-        <v>사업개발처</v>
+        <v>사업계획처</v>
       </c>
       <c r="H120" t="str">
-        <v>개발2부</v>
+        <v>사업계획부</v>
       </c>
       <c r="I120" t="str">
-        <v>사업개발처 개발2부</v>
+        <v>사업계획처 사업계획부</v>
       </c>
       <c r="J120" t="str">
         <v>지정제안</v>
       </c>
       <c r="K120" t="str">
-        <v>업무개선</v>
+        <v>AI혁신</v>
       </c>
       <c r="L120" t="str">
-        <v>[지정제안] 설계용역 과업변경에 따른 계약금액 조정기준 마련</v>
+        <v>[지정제안] AI 기반 도시개발 조감도 및 공간 시각화 프로세스 구축</v>
       </c>
       <c r="M120" t="str">
         <v>개발사업본부</v>
       </c>
       <c r="N120" t="str">
-        <v>사업개발처</v>
+        <v>사업계획처</v>
       </c>
       <c r="O120" t="str">
-        <v>개발2부</v>
+        <v>사업계획부</v>
       </c>
       <c r="P120" t="str">
-        <v>사업개발처 개발 2부</v>
+        <v>사업계획처 사업계획부</v>
       </c>
       <c r="Q120" t="str">
         <v/>
@@ -8224,70 +8219,69 @@
         <v/>
       </c>
     </row>
-    <row r="121" xml:space="preserve">
+    <row r="121">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C121" t="str">
-        <v>2026-08-31 16:05:00</v>
+        <v>2026-08-31 16:40:00</v>
       </c>
       <c r="D121" t="str">
-        <v>김상철</v>
+        <v>박태준</v>
       </c>
       <c r="E121" t="str">
-        <v>기술5급</v>
+        <v>기술6급</v>
       </c>
       <c r="F121" t="str">
-        <v>경영부문</v>
+        <v>개발사업본부</v>
       </c>
       <c r="G121" t="str">
-        <v>경영지원실</v>
+        <v>사업개발처</v>
       </c>
       <c r="H121" t="str">
-        <v>재무부</v>
+        <v>개발1부</v>
       </c>
       <c r="I121" t="str">
-        <v>시설운영부</v>
+        <v>사업개발처 개발1부</v>
       </c>
       <c r="J121" t="str">
         <v>지정제안</v>
       </c>
       <c r="K121" t="str">
-        <v>시설개선</v>
+        <v>안전</v>
       </c>
       <c r="L121" t="str">
-        <v>시스템에어컨 실외기 차양막(커버) 설치</v>
+        <v>중장비·근로자 양방향 스마트 조끼 도입을 통한 사각지대 안전사고 예방</v>
       </c>
       <c r="M121" t="str">
-        <v>운영관리본부</v>
+        <v>개발사업본부</v>
       </c>
       <c r="N121" t="str">
-        <v>시설관리처</v>
+        <v>사업개발처</v>
       </c>
       <c r="O121" t="str">
-        <v>시설운영부</v>
+        <v>개발1부</v>
       </c>
       <c r="P121" t="str">
-        <v>시설관리처 시설운영부</v>
+        <v>사업개발처 개발 1부</v>
       </c>
       <c r="Q121" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R121" t="str">
         <v/>
       </c>
       <c r="S121" t="str">
-        <v>중복 가능성 높음(채택)</v>
-      </c>
-      <c r="T121" t="str" xml:space="preserve">
-        <v xml:space="preserve">공영주차장 정산소 에어컨 실외기 커버 설치_x000d_
-심사결과: 채택 [2021년 제안!I55, 연번 52]</v>
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
       </c>
       <c r="U121" t="str">
-        <v>공영주차장 정산소 에어컨 실외기 커버 제안은 2021년 제안 시트 55행에서 채택으로 확인됨. 실외기 상부 햇빛 차단으로 냉방효율·전기료를 개선하는 수단과 효과가 같음. 정산소에서 별관·체육관동 옥상으로 장소가 바뀌고 통풍·반사재 선택을 보완한 점은 별도 검토 필요.</v>
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -8295,49 +8289,49 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C122" t="str">
-        <v>2026-08-31 16:06:00</v>
+        <v>2026-08-31 16:45:00</v>
       </c>
       <c r="D122" t="str">
-        <v>김효정</v>
+        <v>유창훈</v>
       </c>
       <c r="E122" t="str">
         <v>기술6급</v>
       </c>
       <c r="F122" t="str">
-        <v>개발사업본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="G122" t="str">
-        <v>사업개발처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="H122" t="str">
-        <v>개발2부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="I122" t="str">
-        <v>사업개발처 개발2부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="J122" t="str">
         <v>지정제안</v>
       </c>
       <c r="K122" t="str">
-        <v>업무개선</v>
+        <v>안전</v>
       </c>
       <c r="L122" t="str">
-        <v>[지정제안] 공사근로자 노무비 청구 및 지급관리 기준 마련</v>
+        <v>과천시 지하연계시설 안전사고 예방을 위한 합동안전캠페인 실시</v>
       </c>
       <c r="M122" t="str">
-        <v>개발사업본부</v>
+        <v>사장 직속</v>
       </c>
       <c r="N122" t="str">
-        <v>사업개발처</v>
+        <v>안전총괄단</v>
       </c>
       <c r="O122" t="str">
-        <v>개발2부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="P122" t="str">
-        <v>사업개발처 개발 2부</v>
+        <v>안전총괄단</v>
       </c>
       <c r="Q122" t="str">
         <v/>
@@ -8355,76 +8349,69 @@
         <v/>
       </c>
     </row>
-    <row r="123" xml:space="preserve">
+    <row r="123">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C123" t="str">
-        <v>2026-08-31 16:16:00</v>
+        <v>2026-08-31 17:06:00</v>
       </c>
       <c r="D123" t="str">
-        <v>이현</v>
+        <v>안석열</v>
       </c>
       <c r="E123" t="str">
-        <v>체육6급</v>
+        <v>체육5급</v>
       </c>
       <c r="F123" t="str">
         <v>운영관리본부</v>
       </c>
       <c r="G123" t="str">
+        <v>시민회관체육운영처</v>
+      </c>
+      <c r="H123" t="str">
+        <v>수영부</v>
+      </c>
+      <c r="I123" t="str">
+        <v>시민회관체육운영처 수영부</v>
+      </c>
+      <c r="J123" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K123" t="str">
+        <v>안전</v>
+      </c>
+      <c r="L123" t="str">
+        <v>회전형 3D 홀로그램 LED 팬을 활용한 수영장 안전이용 안내</v>
+      </c>
+      <c r="M123" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N123" t="str">
         <v>시설관리처</v>
       </c>
-      <c r="H123" t="str">
+      <c r="O123" t="str">
         <v>시설운영부</v>
       </c>
-      <c r="I123" t="str">
-        <v>경영지원실 재무부</v>
-      </c>
-      <c r="J123" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K123" t="str">
-        <v>AI혁신</v>
-      </c>
-      <c r="L123" t="str">
-        <v>[지정제안] AI 체육시설 홈페이지 맞춤형 챗봇 도입</v>
-      </c>
-      <c r="M123" t="str">
-        <v>경영부문</v>
-      </c>
-      <c r="N123" t="str">
-        <v>미래전략실</v>
-      </c>
-      <c r="O123" t="str">
-        <v>스마트정보부</v>
-      </c>
       <c r="P123" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시설관리처 시설운영부</v>
       </c>
       <c r="Q123" t="str">
-        <v>중복</v>
+        <v/>
       </c>
       <c r="R123" t="str">
-        <v>2026-121 카카오톡 챗봇 연계형 보이는 ARS 서비스 구축</v>
+        <v/>
       </c>
       <c r="S123" t="str">
-        <v>중복접수(2026)</v>
-      </c>
-      <c r="T123" t="str" xml:space="preserve">
-        <v xml:space="preserve">2026 게시판 121 카카오톡 챗봇 연계형 보이는 ARS 서비스 구축_x000d_
-채택결과 미확인 [Sheet1!M113:N113]_x000d_
-_x000d_
-2024-07-096 디지털 플랫폼 정부구현을 위한 스마트 공공기관 챗봇 도입_x000d_
-심사결과: 불채택 [2024년 제안!I201]_x000d_
-_x000d_
-2025-06-065 도시공사 민원업무 효율화를 위한 AI 자동응답 시스템 도입_x000d_
-심사결과: 과락3명 [2025년 제안 총괄 !I56]</v>
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
       </c>
       <c r="U123" t="str">
-        <v>기존 중복(2026) 표시를 재검토함. 게시판 121번은 평점·과락구분이 비어 있어 채택을 확인할 수 없음. 별도 과거 챗봇 비교안도 각각 불채택·과락3명임. 제목·자동응대 기능만으로 채택된 제안과 중복이라고 할 수 없어 기존 중복 표시는 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -8432,28 +8419,28 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C124" t="str">
-        <v>2026-08-31 16:22:00</v>
+        <v>2026-08-31 18:20:00</v>
       </c>
       <c r="D124" t="str">
-        <v>박소원</v>
+        <v>정재우</v>
       </c>
       <c r="E124" t="str">
-        <v>기술6급</v>
+        <v>업무직</v>
       </c>
       <c r="F124" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G124" t="str">
-        <v>미래전략실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H124" t="str">
-        <v>스마트정보부</v>
+        <v>빙상부</v>
       </c>
       <c r="I124" t="str">
-        <v>미래전략실 스마트보부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J124" t="str">
         <v>지정제안</v>
@@ -8462,19 +8449,19 @@
         <v>안전</v>
       </c>
       <c r="L124" t="str">
-        <v>[지정제안] AI 기반 실시간 인원관리시스템을 활용한 체육시설 안전관리 강화</v>
+        <v>링크장 출입문 내 주의사항</v>
       </c>
       <c r="M124" t="str">
-        <v>사장 직속</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N124" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O124" t="str">
-        <v>안전총괄단</v>
+        <v>빙상부</v>
       </c>
       <c r="P124" t="str">
-        <v>안전총괄단</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q124" t="str">
         <v/>
@@ -8497,49 +8484,49 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C125" t="str">
-        <v>2026-08-31 16:25:00</v>
+        <v>2026-08-31 18:23:00</v>
       </c>
       <c r="D125" t="str">
-        <v>박소원</v>
+        <v>변정환</v>
       </c>
       <c r="E125" t="str">
-        <v>기술6급</v>
+        <v>업무직</v>
       </c>
       <c r="F125" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G125" t="str">
-        <v>미래전략실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H125" t="str">
-        <v>스마트정보부</v>
+        <v>빙상부</v>
       </c>
       <c r="I125" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="J125" t="str">
         <v>지정제안</v>
       </c>
       <c r="K125" t="str">
-        <v>AI혁신</v>
+        <v>안전</v>
       </c>
       <c r="L125" t="str">
-        <v>[지정제안] 개인정보 수집·이용 동의서 점검 에이전트 구축</v>
+        <v>시니어 안전지킴이</v>
       </c>
       <c r="M125" t="str">
-        <v>경영부문</v>
+        <v>운영관리본부</v>
       </c>
       <c r="N125" t="str">
-        <v>미래전략실</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="O125" t="str">
-        <v>스마트정보부</v>
+        <v>빙상부</v>
       </c>
       <c r="P125" t="str">
-        <v>미래전략실 스마트정보부</v>
+        <v>시민회관체육운영처 빙상부</v>
       </c>
       <c r="Q125" t="str">
         <v/>
@@ -8557,54 +8544,54 @@
         <v/>
       </c>
     </row>
-    <row r="126">
+    <row r="126" xml:space="preserve">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C126" t="str">
-        <v>2026-08-31 16:31:00</v>
+        <v>2026-08-31 18:43:00</v>
       </c>
       <c r="D126" t="str">
-        <v>최윤호</v>
+        <v>최성훈</v>
       </c>
       <c r="E126" t="str">
-        <v>기술6급</v>
+        <v>체육4급</v>
       </c>
       <c r="F126" t="str">
-        <v>개발사업본부</v>
+        <v>운영관리본부</v>
       </c>
       <c r="G126" t="str">
-        <v>사업개발처</v>
+        <v>시민회관체육운영처</v>
       </c>
       <c r="H126" t="str">
-        <v>기술지원부</v>
+        <v>여가체육부</v>
       </c>
       <c r="I126" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>시민회관체육운영처 여가체육부</v>
       </c>
       <c r="J126" t="str">
         <v>지정제안</v>
       </c>
       <c r="K126" t="str">
-        <v>AI혁신</v>
+        <v>지역상생</v>
       </c>
       <c r="L126" t="str">
-        <v>[지정제안] 설계변경 실정보고 등 오류 파악을 위한 AI감리 도입</v>
+        <v>잔디마당 과천시 상인 프리 마켓 운영</v>
       </c>
       <c r="M126" t="str">
-        <v>개발사업본부</v>
+        <v>경영부문</v>
       </c>
       <c r="N126" t="str">
-        <v>사업개발처</v>
+        <v>경영지원실</v>
       </c>
       <c r="O126" t="str">
-        <v>기술지원부</v>
+        <v>총무행정부</v>
       </c>
       <c r="P126" t="str">
-        <v>사업개발처 기술지원부</v>
+        <v>경영지원실 총무행정부</v>
       </c>
       <c r="Q126" t="str">
         <v/>
@@ -8613,1133 +8600,612 @@
         <v/>
       </c>
       <c r="S126" t="str">
-        <v/>
-      </c>
-      <c r="T126" t="str">
-        <v/>
-      </c>
-      <c r="U126" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127">
-        <v>126</v>
-      </c>
-      <c r="B127" t="str">
-        <v>135</v>
-      </c>
-      <c r="C127" t="str">
-        <v>2026-08-31 16:36:00</v>
-      </c>
-      <c r="D127" t="str">
-        <v>한효진</v>
-      </c>
-      <c r="E127" t="str">
-        <v>기술6급</v>
-      </c>
-      <c r="F127" t="str">
-        <v>개발사업본부</v>
-      </c>
-      <c r="G127" t="str">
-        <v>사업계획처</v>
-      </c>
-      <c r="H127" t="str">
-        <v>사업계획부</v>
-      </c>
-      <c r="I127" t="str">
-        <v>사업계획처 사업계획부</v>
-      </c>
-      <c r="J127" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K127" t="str">
-        <v>AI혁신</v>
-      </c>
-      <c r="L127" t="str">
-        <v>[지정제안] AI 기반 도시개발 조감도 및 공간 시각화 프로세스 구축</v>
-      </c>
-      <c r="M127" t="str">
-        <v>개발사업본부</v>
-      </c>
-      <c r="N127" t="str">
-        <v>사업계획처</v>
-      </c>
-      <c r="O127" t="str">
-        <v>사업계획부</v>
-      </c>
-      <c r="P127" t="str">
-        <v>사업계획처 사업계획부</v>
-      </c>
-      <c r="Q127" t="str">
-        <v/>
-      </c>
-      <c r="R127" t="str">
-        <v/>
-      </c>
-      <c r="S127" t="str">
-        <v/>
-      </c>
-      <c r="T127" t="str">
-        <v/>
-      </c>
-      <c r="U127" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128">
-        <v>127</v>
-      </c>
-      <c r="B128" t="str">
-        <v>136</v>
-      </c>
-      <c r="C128" t="str">
-        <v>2026-08-31 16:40:00</v>
-      </c>
-      <c r="D128" t="str">
-        <v>박태준</v>
-      </c>
-      <c r="E128" t="str">
-        <v>기술6급</v>
-      </c>
-      <c r="F128" t="str">
-        <v>개발사업본부</v>
-      </c>
-      <c r="G128" t="str">
-        <v>사업개발처</v>
-      </c>
-      <c r="H128" t="str">
-        <v>개발1부</v>
-      </c>
-      <c r="I128" t="str">
-        <v>사업개발처 개발1부</v>
-      </c>
-      <c r="J128" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K128" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L128" t="str">
-        <v>중장비·근로자 양방향 스마트 조끼 도입을 통한 사각지대 안전사고 예방</v>
-      </c>
-      <c r="M128" t="str">
-        <v>개발사업본부</v>
-      </c>
-      <c r="N128" t="str">
-        <v>사업개발처</v>
-      </c>
-      <c r="O128" t="str">
-        <v>개발1부</v>
-      </c>
-      <c r="P128" t="str">
-        <v>사업개발처 개발 1부</v>
-      </c>
-      <c r="Q128" t="str">
-        <v/>
-      </c>
-      <c r="R128" t="str">
-        <v/>
-      </c>
-      <c r="S128" t="str">
-        <v/>
-      </c>
-      <c r="T128" t="str">
-        <v/>
-      </c>
-      <c r="U128" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129">
-        <v>128</v>
-      </c>
-      <c r="B129" t="str">
-        <v>137</v>
-      </c>
-      <c r="C129" t="str">
-        <v>2026-08-31 16:45:00</v>
-      </c>
-      <c r="D129" t="str">
-        <v>유창훈</v>
-      </c>
-      <c r="E129" t="str">
-        <v>기술6급</v>
-      </c>
-      <c r="F129" t="str">
-        <v>사장 직속</v>
-      </c>
-      <c r="G129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="H129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="I129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="J129" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K129" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L129" t="str">
-        <v>과천시 지하연계시설 안전사고 예방을 위한 합동안전캠페인 실시</v>
-      </c>
-      <c r="M129" t="str">
-        <v>사장 직속</v>
-      </c>
-      <c r="N129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="O129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="P129" t="str">
-        <v>안전총괄단</v>
-      </c>
-      <c r="Q129" t="str">
-        <v/>
-      </c>
-      <c r="R129" t="str">
-        <v/>
-      </c>
-      <c r="S129" t="str">
-        <v/>
-      </c>
-      <c r="T129" t="str">
-        <v/>
-      </c>
-      <c r="U129" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130">
-        <v>129</v>
-      </c>
-      <c r="B130" t="str">
-        <v>138</v>
-      </c>
-      <c r="C130" t="str">
-        <v>2026-08-31 17:06:00</v>
-      </c>
-      <c r="D130" t="str">
-        <v>안석열</v>
-      </c>
-      <c r="E130" t="str">
-        <v>체육5급</v>
-      </c>
-      <c r="F130" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G130" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H130" t="str">
-        <v>수영부</v>
-      </c>
-      <c r="I130" t="str">
-        <v>시민회관체육운영처 수영부</v>
-      </c>
-      <c r="J130" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K130" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L130" t="str">
-        <v>회전형 3D 홀로그램 LED 팬을 활용한 수영장 안전이용 안내</v>
-      </c>
-      <c r="M130" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N130" t="str">
-        <v>시설관리처</v>
-      </c>
-      <c r="O130" t="str">
-        <v>시설운영부</v>
-      </c>
-      <c r="P130" t="str">
-        <v>시설관리처 시설운영부</v>
-      </c>
-      <c r="Q130" t="str">
-        <v/>
-      </c>
-      <c r="R130" t="str">
-        <v/>
-      </c>
-      <c r="S130" t="str">
-        <v/>
-      </c>
-      <c r="T130" t="str">
-        <v/>
-      </c>
-      <c r="U130" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131">
-        <v>130</v>
-      </c>
-      <c r="B131" t="str">
-        <v>139</v>
-      </c>
-      <c r="C131" t="str">
-        <v>2026-08-31 18:20:00</v>
-      </c>
-      <c r="D131" t="str">
-        <v>정재우</v>
-      </c>
-      <c r="E131" t="str">
-        <v>업무직</v>
-      </c>
-      <c r="F131" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G131" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H131" t="str">
-        <v>빙상부</v>
-      </c>
-      <c r="I131" t="str">
-        <v>시민회관체육운영처 빙상부</v>
-      </c>
-      <c r="J131" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K131" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L131" t="str">
-        <v>링크장 출입문 내 주의사항</v>
-      </c>
-      <c r="M131" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N131" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="O131" t="str">
-        <v>빙상부</v>
-      </c>
-      <c r="P131" t="str">
-        <v>시민회관체육운영처 빙상부</v>
-      </c>
-      <c r="Q131" t="str">
-        <v/>
-      </c>
-      <c r="R131" t="str">
-        <v/>
-      </c>
-      <c r="S131" t="str">
-        <v/>
-      </c>
-      <c r="T131" t="str">
-        <v/>
-      </c>
-      <c r="U131" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132">
-        <v>131</v>
-      </c>
-      <c r="B132" t="str">
-        <v>140</v>
-      </c>
-      <c r="C132" t="str">
-        <v>2026-08-31 18:23:00</v>
-      </c>
-      <c r="D132" t="str">
-        <v>변정환</v>
-      </c>
-      <c r="E132" t="str">
-        <v>업무직</v>
-      </c>
-      <c r="F132" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G132" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H132" t="str">
-        <v>빙상부</v>
-      </c>
-      <c r="I132" t="str">
-        <v>시민회관체육운영처 빙상부</v>
-      </c>
-      <c r="J132" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K132" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L132" t="str">
-        <v>시니어 안전지킴이</v>
-      </c>
-      <c r="M132" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N132" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="O132" t="str">
-        <v>빙상부</v>
-      </c>
-      <c r="P132" t="str">
-        <v>시민회관체육운영처 빙상부</v>
-      </c>
-      <c r="Q132" t="str">
-        <v/>
-      </c>
-      <c r="R132" t="str">
-        <v/>
-      </c>
-      <c r="S132" t="str">
-        <v/>
-      </c>
-      <c r="T132" t="str">
-        <v/>
-      </c>
-      <c r="U132" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="133" xml:space="preserve">
-      <c r="A133">
-        <v>132</v>
-      </c>
-      <c r="B133" t="str">
-        <v>141</v>
-      </c>
-      <c r="C133" t="str">
-        <v>2026-08-31 18:35:00</v>
-      </c>
-      <c r="D133" t="str">
-        <v>조홍원</v>
-      </c>
-      <c r="E133" t="str">
-        <v>체육5급</v>
-      </c>
-      <c r="F133" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G133" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H133" t="str">
-        <v>여가체육부</v>
-      </c>
-      <c r="I133" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
-      </c>
-      <c r="J133" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K133" t="str">
-        <v>안전</v>
-      </c>
-      <c r="L133" t="str">
-        <v>QR코드를 활용한 "운동 전 자가 안전 확인제" 도입</v>
-      </c>
-      <c r="M133" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N133" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="O133" t="str">
-        <v>여가체육부</v>
-      </c>
-      <c r="P133" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
-      </c>
-      <c r="Q133" t="str">
-        <v>중복</v>
-      </c>
-      <c r="R133" t="str">
-        <v>2026-75 운동 전 10초! 자가안전확인제 운영</v>
-      </c>
-      <c r="S133" t="str">
-        <v>중복접수(2026)</v>
-      </c>
-      <c r="T133" t="str" xml:space="preserve">
-        <v xml:space="preserve">2026 게시판 75 운동 전 10초! 자가안전확인제 운영_x000d_
-채택결과 미확인 [Sheet1!M67:N67]</v>
-      </c>
-      <c r="U133" t="str">
-        <v>기존 중복(2026) 표시를 재검토함. 자가확인 증상·QR 안내·운동 자제 방식은 유사하지만 게시판 75번의 평점·과락구분이 비어 있어 채택을 확인할 수 없음. 현재 접수 제안끼리의 유사성과 채택안 중복은 구분해야 하므로 보류로 수정함. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
-      </c>
-    </row>
-    <row r="134" xml:space="preserve">
-      <c r="A134">
-        <v>133</v>
-      </c>
-      <c r="B134" t="str">
-        <v>142</v>
-      </c>
-      <c r="C134" t="str">
-        <v>2026-08-31 18:43:00</v>
-      </c>
-      <c r="D134" t="str">
-        <v>최성훈</v>
-      </c>
-      <c r="E134" t="str">
-        <v>체육4급</v>
-      </c>
-      <c r="F134" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G134" t="str">
-        <v>시민회관체육운영처</v>
-      </c>
-      <c r="H134" t="str">
-        <v>여가체육부</v>
-      </c>
-      <c r="I134" t="str">
-        <v>시민회관체육운영처 여가체육부</v>
-      </c>
-      <c r="J134" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K134" t="str">
-        <v>지역상생</v>
-      </c>
-      <c r="L134" t="str">
-        <v>잔디마당 과천시 상인 프리 마켓 운영</v>
-      </c>
-      <c r="M134" t="str">
-        <v>경영부문</v>
-      </c>
-      <c r="N134" t="str">
-        <v>경영지원실</v>
-      </c>
-      <c r="O134" t="str">
-        <v>총무행정부</v>
-      </c>
-      <c r="P134" t="str">
-        <v>경영지원실 총무행정부</v>
-      </c>
-      <c r="Q134" t="str">
-        <v/>
-      </c>
-      <c r="R134" t="str">
-        <v/>
-      </c>
-      <c r="S134" t="str">
         <v>판단보류(채택결과 미확인)</v>
       </c>
-      <c r="T134" t="str" xml:space="preserve">
+      <c r="T126" t="str" xml:space="preserve">
         <v xml:space="preserve">2023-07-054 자원선순환 활성화 플리마켓 개최_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]_x000d_
 _x000d_
 2022-12-241 직원 중고장터 &amp; 플리마켓 활성화_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]</v>
       </c>
-      <c r="U134" t="str">
+      <c r="U126" t="str">
         <v>비교한 두 플리마켓 제안은 채택결과를 확인할 수 없음. 직원 중고물품·자원순환 행사와 이번 지역상인 판로 지원은 참여자·물품·목적에도 차이가 있음. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135">
-        <v>134</v>
-      </c>
-      <c r="B135" t="str">
+    <row r="127">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
         <v>143</v>
       </c>
-      <c r="C135" t="str">
+      <c r="C127" t="str">
         <v>2026-08-31 21:27:00</v>
       </c>
-      <c r="D135" t="str">
+      <c r="D127" t="str">
         <v>조은희</v>
       </c>
-      <c r="E135" t="str">
+      <c r="E127" t="str">
         <v>기술5급</v>
       </c>
-      <c r="F135" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G135" t="str">
+      <c r="F127" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G127" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="H135" t="str">
+      <c r="H127" t="str">
         <v>수련관운영부</v>
       </c>
-      <c r="I135" t="str">
+      <c r="I127" t="str">
         <v>공원수련관관리처 수련관운영부</v>
       </c>
-      <c r="J135" t="str">
-        <v>지정제안</v>
-      </c>
-      <c r="K135" t="str">
+      <c r="J127" t="str">
+        <v>지정제안</v>
+      </c>
+      <c r="K127" t="str">
         <v>업무개선</v>
       </c>
-      <c r="L135" t="str">
+      <c r="L127" t="str">
         <v>AI를 활용한 QR코드 및 GPS 기반 셔틀버스 비정규직 근로자 복무관리 자동화</v>
       </c>
-      <c r="M135" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N135" t="str">
+      <c r="M127" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N127" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="O135" t="str">
+      <c r="O127" t="str">
         <v>수련관운영부</v>
       </c>
-      <c r="P135" t="str">
+      <c r="P127" t="str">
         <v>공원수련관관리처 수련관운영부</v>
       </c>
-      <c r="Q135" t="str">
-        <v/>
-      </c>
-      <c r="R135" t="str">
-        <v/>
-      </c>
-      <c r="S135" t="str">
-        <v/>
-      </c>
-      <c r="T135" t="str">
-        <v/>
-      </c>
-      <c r="U135" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136">
-        <v>135</v>
-      </c>
-      <c r="B136" t="str">
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
         <v>144</v>
       </c>
-      <c r="C136" t="str">
+      <c r="C128" t="str">
         <v>2026-09-10 10:14:00</v>
       </c>
-      <c r="D136" t="str">
+      <c r="D128" t="str">
         <v>최성근</v>
       </c>
-      <c r="E136" t="str">
+      <c r="E128" t="str">
         <v>기술 6급</v>
       </c>
-      <c r="F136" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G136" t="str">
+      <c r="F128" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G128" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="H136" t="str">
+      <c r="H128" t="str">
         <v>시설지원부</v>
       </c>
-      <c r="I136" t="str">
+      <c r="I128" t="str">
         <v>공원수련관관리처 시설지원부</v>
       </c>
-      <c r="J136" t="str">
+      <c r="J128" t="str">
         <v>실행제안</v>
       </c>
-      <c r="K136" t="str">
+      <c r="K128" t="str">
         <v>안전</v>
       </c>
-      <c r="L136" t="str">
+      <c r="L128" t="str">
         <v>(실행제안) 관문체육공원 태양광 발전시설 하부 안전보호재 설치</v>
       </c>
-      <c r="M136" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N136" t="str">
+      <c r="M128" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N128" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="O136" t="str">
+      <c r="O128" t="str">
         <v>시설지원부</v>
       </c>
-      <c r="P136" t="str">
+      <c r="P128" t="str">
         <v>공원수련관관리처 시설지원부</v>
       </c>
-      <c r="Q136" t="str">
-        <v/>
-      </c>
-      <c r="R136" t="str">
-        <v/>
-      </c>
-      <c r="S136" t="str">
-        <v/>
-      </c>
-      <c r="T136" t="str">
-        <v/>
-      </c>
-      <c r="U136" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137">
-        <v>136</v>
-      </c>
-      <c r="B137" t="str">
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
         <v>146</v>
       </c>
-      <c r="C137" t="str">
+      <c r="C129" t="str">
         <v>2026-09-23 16:58:00</v>
       </c>
-      <c r="D137" t="str">
+      <c r="D129" t="str">
         <v>김재범</v>
       </c>
-      <c r="E137" t="str">
+      <c r="E129" t="str">
         <v>체육5급</v>
       </c>
-      <c r="F137" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G137" t="str">
+      <c r="F129" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G129" t="str">
         <v>시민회관체육운영처</v>
       </c>
-      <c r="H137" t="str">
+      <c r="H129" t="str">
         <v>여가체육부</v>
       </c>
-      <c r="I137" t="str">
+      <c r="I129" t="str">
         <v>시민회관체육운영처 여가체육부</v>
       </c>
-      <c r="J137" t="str">
+      <c r="J129" t="str">
         <v>자유제안</v>
       </c>
-      <c r="K137" t="str">
+      <c r="K129" t="str">
         <v>시설개선</v>
       </c>
-      <c r="L137" t="str">
+      <c r="L129" t="str">
         <v>장애인 주차구역 스마트단속시스템</v>
       </c>
-      <c r="M137" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N137" t="str">
+      <c r="M129" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N129" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="O137" t="str">
+      <c r="O129" t="str">
         <v>시설지원부</v>
       </c>
-      <c r="P137" t="str">
+      <c r="P129" t="str">
         <v>공원수련관관리처 시설지원부</v>
       </c>
-      <c r="Q137" t="str">
-        <v/>
-      </c>
-      <c r="R137" t="str">
-        <v/>
-      </c>
-      <c r="S137" t="str">
-        <v/>
-      </c>
-      <c r="T137" t="str">
-        <v/>
-      </c>
-      <c r="U137" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138">
-        <v>137</v>
-      </c>
-      <c r="B138" t="str">
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
         <v>147</v>
       </c>
-      <c r="C138" t="str">
+      <c r="C130" t="str">
         <v>2026-10-01 10:18:00</v>
       </c>
-      <c r="D138" t="str">
+      <c r="D130" t="str">
         <v>성화진</v>
       </c>
-      <c r="E138" t="str">
+      <c r="E130" t="str">
         <v>기술6급</v>
       </c>
-      <c r="F138" t="str">
+      <c r="F130" t="str">
         <v>사장 직속</v>
       </c>
-      <c r="G138" t="str">
+      <c r="G130" t="str">
         <v>안전총괄단</v>
       </c>
-      <c r="H138" t="str">
+      <c r="H130" t="str">
         <v>안전총괄단</v>
       </c>
-      <c r="I138" t="str">
+      <c r="I130" t="str">
         <v>안전총괄단</v>
       </c>
-      <c r="J138" t="str">
+      <c r="J130" t="str">
         <v>자유제안</v>
       </c>
-      <c r="K138" t="str">
+      <c r="K130" t="str">
         <v>업무개선</v>
       </c>
-      <c r="L138" t="str">
+      <c r="L130" t="str">
         <v>사원증 QR을 활용한 디지털 명함 도입 및 종이명함 제작 최소화</v>
       </c>
-      <c r="M138" t="str">
+      <c r="M130" t="str">
         <v>경영부문</v>
       </c>
-      <c r="N138" t="str">
+      <c r="N130" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="O138" t="str">
+      <c r="O130" t="str">
         <v>총무행정부</v>
       </c>
-      <c r="P138" t="str">
+      <c r="P130" t="str">
         <v>경영지원실 총무행정부</v>
       </c>
-      <c r="Q138" t="str">
-        <v/>
-      </c>
-      <c r="R138" t="str">
-        <v/>
-      </c>
-      <c r="S138" t="str">
-        <v/>
-      </c>
-      <c r="T138" t="str">
-        <v/>
-      </c>
-      <c r="U138" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="139" xml:space="preserve">
-      <c r="A139">
-        <v>138</v>
-      </c>
-      <c r="B139" t="str">
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131" xml:space="preserve">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="str">
         <v>148</v>
       </c>
-      <c r="C139" t="str">
+      <c r="C131" t="str">
         <v>2026-10-15 14:40:00</v>
       </c>
-      <c r="D139" t="str">
+      <c r="D131" t="str">
         <v>조아라</v>
       </c>
-      <c r="E139" t="str">
+      <c r="E131" t="str">
         <v>체육6급</v>
       </c>
-      <c r="F139" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G139" t="str">
+      <c r="F131" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G131" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="H139" t="str">
+      <c r="H131" t="str">
         <v>공원운영부</v>
       </c>
-      <c r="I139" t="str">
+      <c r="I131" t="str">
         <v>공원수련관관리처 공원운영부</v>
       </c>
-      <c r="J139" t="str">
+      <c r="J131" t="str">
         <v>실행제안</v>
       </c>
-      <c r="K139" t="str">
+      <c r="K131" t="str">
         <v>시설개선</v>
       </c>
-      <c r="L139" t="str">
+      <c r="L131" t="str">
         <v>관문실내체육관 배드민턴 고정식 지주대 설치</v>
       </c>
-      <c r="M139" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N139" t="str">
+      <c r="M131" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N131" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="O139" t="str">
+      <c r="O131" t="str">
         <v>공원운영부</v>
       </c>
-      <c r="P139" t="str">
+      <c r="P131" t="str">
         <v>공원수련관관리처 공원운영부</v>
       </c>
-      <c r="Q139" t="str">
-        <v/>
-      </c>
-      <c r="R139" t="str">
-        <v/>
-      </c>
-      <c r="S139" t="str">
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
         <v>유사(채택)</v>
       </c>
-      <c r="T139" t="str" xml:space="preserve">
+      <c r="T131" t="str" xml:space="preserve">
         <v xml:space="preserve">배드민턴 지줏대 모서리 보호대 설치_x000d_
 심사결과: 채택 [2021년 제안!I199, 연번 196]</v>
       </c>
-      <c r="U139" t="str">
+      <c r="U131" t="str">
         <v>같은 제안자 조아라의 지줏대 모서리 보호대 설치는 2021년 제안 시트 199행에서 채택으로 확인됨. 안전 목적과 대상은 같지만 이번은 이동식 보호대 부착 대신 바닥 타공 후 고정식 지주대로 전환하여 이동·정리 위험까지 줄이는 구조 개선임. 과거 첨부 원문과 차별성 확인 필요.</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140">
-        <v>139</v>
-      </c>
-      <c r="B140" t="str">
+    <row r="132">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="str">
         <v>150</v>
       </c>
-      <c r="C140" t="str">
+      <c r="C132" t="str">
         <v>2026-10-19 15:05:00</v>
       </c>
-      <c r="D140" t="str">
+      <c r="D132" t="str">
         <v>김민정</v>
       </c>
-      <c r="E140" t="str">
+      <c r="E132" t="str">
         <v>체육6급</v>
       </c>
-      <c r="F140" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G140" t="str">
+      <c r="F132" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G132" t="str">
         <v>시민회관체육운영처</v>
       </c>
-      <c r="H140" t="str">
+      <c r="H132" t="str">
         <v>수영부</v>
       </c>
-      <c r="I140" t="str">
+      <c r="I132" t="str">
         <v>시민회관체육운영처 수영부</v>
       </c>
-      <c r="J140" t="str">
+      <c r="J132" t="str">
         <v>업무제안</v>
       </c>
-      <c r="K140" t="str">
+      <c r="K132" t="str">
         <v>업무개선</v>
       </c>
-      <c r="L140" t="str">
+      <c r="L132" t="str">
         <v>수영장 샤워기 번호표 부착 제작</v>
       </c>
-      <c r="M140" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N140" t="str">
+      <c r="M132" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N132" t="str">
         <v>시민회관체육운영처</v>
       </c>
-      <c r="O140" t="str">
+      <c r="O132" t="str">
         <v>여가체육부</v>
       </c>
-      <c r="P140" t="str">
+      <c r="P132" t="str">
         <v>시민회관체육운영처 여가체육부</v>
       </c>
-      <c r="Q140" t="str">
-        <v/>
-      </c>
-      <c r="R140" t="str">
-        <v/>
-      </c>
-      <c r="S140" t="str">
-        <v/>
-      </c>
-      <c r="T140" t="str">
-        <v/>
-      </c>
-      <c r="U140" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="141" xml:space="preserve">
-      <c r="A141">
-        <v>140</v>
-      </c>
-      <c r="B141" t="str">
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133" xml:space="preserve">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="str">
         <v>152</v>
       </c>
-      <c r="C141" t="str">
+      <c r="C133" t="str">
         <v>2026-10-21 09:24:00</v>
       </c>
-      <c r="D141" t="str">
+      <c r="D133" t="str">
         <v>이승진</v>
       </c>
-      <c r="E141" t="str">
+      <c r="E133" t="str">
         <v>기술 6급</v>
       </c>
-      <c r="F141" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="G141" t="str">
+      <c r="F133" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="G133" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="H141" t="str">
+      <c r="H133" t="str">
         <v>시설지원부</v>
       </c>
-      <c r="I141" t="str">
+      <c r="I133" t="str">
         <v>공원수련관관리처 시설지원부</v>
       </c>
-      <c r="J141" t="str">
+      <c r="J133" t="str">
         <v>실행제안</v>
       </c>
-      <c r="K141" t="str">
+      <c r="K133" t="str">
         <v>예산절감(수익창출)</v>
       </c>
-      <c r="L141" t="str">
+      <c r="L133" t="str">
         <v>관문실내체육관 자폐식 샤워수전 수동스탑 부품 교체를 통한 절수 제안</v>
       </c>
-      <c r="M141" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N141" t="str">
+      <c r="M133" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N133" t="str">
         <v>공원수련관관리처</v>
       </c>
-      <c r="O141" t="str">
+      <c r="O133" t="str">
         <v>시설지원부</v>
       </c>
-      <c r="P141" t="str">
+      <c r="P133" t="str">
         <v>공원수련관관리처 시설지원부</v>
       </c>
-      <c r="Q141" t="str">
-        <v/>
-      </c>
-      <c r="R141" t="str">
-        <v/>
-      </c>
-      <c r="S141" t="str">
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
         <v>판단보류(채택결과 미확인)</v>
       </c>
-      <c r="T141" t="str" xml:space="preserve">
+      <c r="T133" t="str" xml:space="preserve">
         <v xml:space="preserve">2021-12-217 절수형 샤워기 설치_x000d_
 심사결과: 부적합(중복) [2022년 제안!G252]_x000d_
 _x000d_
 2022-12-328 반응형 절수 장치 설치를 통한 수자원 절약_x000d_
 채택결과 확인 불가 [제안 본문에 심사결과 없음]</v>
       </c>
-      <c r="U141" t="str">
+      <c r="U133" t="str">
         <v>2021-12-217은 부적합(중복)으로 채택안이 아니며, 2022-12-328은 채택결과를 확인할 수 없음. 이번 수동 중간차단 방식은 절수형 유량저감·반응형 수전과 작동원리도 다름. 제공 자료에서 채택 근거가 확인되지 않으므로 채택안과의 중복으로 확정하지 않음.</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142">
-        <v>141</v>
-      </c>
-      <c r="B142" t="str">
+    <row r="134">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="str">
         <v>153</v>
       </c>
-      <c r="C142" t="str">
+      <c r="C134" t="str">
         <v>2026-10-21 10:44:00</v>
       </c>
-      <c r="D142" t="str">
+      <c r="D134" t="str">
         <v>우세림</v>
       </c>
-      <c r="E142" t="str">
+      <c r="E134" t="str">
         <v>체육6급</v>
       </c>
-      <c r="F142" t="str">
+      <c r="F134" t="str">
         <v>경영부문</v>
       </c>
-      <c r="G142" t="str">
+      <c r="G134" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="H142" t="str">
+      <c r="H134" t="str">
         <v>총무행정부</v>
       </c>
-      <c r="I142" t="str">
+      <c r="I134" t="str">
         <v>경영지원실 총무행정부</v>
       </c>
-      <c r="J142" t="str">
+      <c r="J134" t="str">
         <v>직무제안</v>
       </c>
-      <c r="K142" t="str">
+      <c r="K134" t="str">
         <v>제도개선</v>
       </c>
-      <c r="L142" t="str">
+      <c r="L134" t="str">
         <v>AI 활용 제안심사 홈페이지 구축을 통한 심사 업무 효율화</v>
       </c>
-      <c r="M142" t="str">
+      <c r="M134" t="str">
         <v>경영부문</v>
       </c>
-      <c r="N142" t="str">
+      <c r="N134" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="O142" t="str">
+      <c r="O134" t="str">
         <v>총무행정부</v>
       </c>
-      <c r="P142" t="str">
+      <c r="P134" t="str">
         <v>경영지원실 총무행정부</v>
       </c>
-      <c r="Q142" t="str">
-        <v/>
-      </c>
-      <c r="R142" t="str">
-        <v/>
-      </c>
-      <c r="S142" t="str">
-        <v/>
-      </c>
-      <c r="T142" t="str">
-        <v/>
-      </c>
-      <c r="U142" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143">
-        <v>142</v>
-      </c>
-      <c r="B143" t="str">
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="str">
         <v>154</v>
       </c>
-      <c r="C143" t="str">
+      <c r="C135" t="str">
         <v>2026-10-22 11:37:00</v>
       </c>
-      <c r="D143" t="str">
+      <c r="D135" t="str">
         <v>나갑성</v>
       </c>
-      <c r="E143" t="str">
+      <c r="E135" t="str">
         <v>기술4급</v>
       </c>
-      <c r="F143" t="str">
+      <c r="F135" t="str">
         <v>경영부문</v>
       </c>
-      <c r="G143" t="str">
+      <c r="G135" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="H143" t="str">
+      <c r="H135" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="I143" t="str">
+      <c r="I135" t="str">
         <v>경영지원실</v>
       </c>
-      <c r="J143" t="str">
+      <c r="J135" t="str">
         <v>자유제안</v>
       </c>
-      <c r="K143" t="str">
+      <c r="K135" t="str">
         <v>업무개선</v>
       </c>
-      <c r="L143" t="str">
+      <c r="L135" t="str">
         <v>완강기 빨간 테이프 부착을 통한 소방시설 시인성 개선 제안</v>
       </c>
-      <c r="M143" t="str">
-        <v>운영관리본부</v>
-      </c>
-      <c r="N143" t="str">
+      <c r="M135" t="str">
+        <v>운영관리본부</v>
+      </c>
+      <c r="N135" t="str">
         <v>시설관리처</v>
       </c>
-      <c r="O143" t="str">
+      <c r="O135" t="str">
         <v>시설운영부</v>
       </c>
-      <c r="P143" t="str">
+      <c r="P135" t="str">
         <v>시설관리처 시설운영부</v>
       </c>
-      <c r="Q143" t="str">
-        <v/>
-      </c>
-      <c r="R143" t="str">
-        <v/>
-      </c>
-      <c r="S143" t="str">
-        <v/>
-      </c>
-      <c r="T143" t="str">
-        <v/>
-      </c>
-      <c r="U143" t="str">
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U135"/>
   </ignoredErrors>
 </worksheet>
 </file>